--- a/Unlock AI Value - content for client review.xlsx
+++ b/Unlock AI Value - content for client review.xlsx
@@ -723,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -806,7 +806,7 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Are you ready to unlock your AI Value?</t>
+          <t>Are you ready to unlock your AI Value in insurance?</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Button (primary)</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1076,17 +1076,17 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Explore</t>
+          <t>Framework screen</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Instruction</t>
+          <t>Button (secondary)</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Tap a value pool to explore</t>
+          <t>Start the diagnostic</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr"/>
@@ -1096,17 +1096,17 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Explore</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Instruction</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>01 / 18</t>
+          <t>Tap a value pool to explore</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr"/>
@@ -1116,17 +1116,17 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Identify</t>
+          <t>Explore</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Headline</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tap your badge</t>
+          <t>Start the diagnostic</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr"/>
@@ -1136,17 +1136,17 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Identify</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Lede</t>
+          <t>Progress</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Your badge carries your role, so the blueprint fits your job.</t>
+          <t>Question 1 of 18</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr"/>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Reader state</t>
+          <t>Headline</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Waiting for badge</t>
+          <t>Tap your badge</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr"/>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Lede</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Enter email manually</t>
+          <t>Your badge carries your role, so the blueprint fits your job.</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr"/>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Reader state</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>See my results</t>
+          <t>Waiting for badge</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr"/>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Enter email manually</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr"/>
@@ -1236,17 +1236,17 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Results 1</t>
+          <t>Identify</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Eyebrow</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Your position</t>
+          <t>See my results</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr"/>
@@ -1256,17 +1256,17 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Results 2</t>
+          <t>Identify</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Eyebrow</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Where you lead, where you lag</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr"/>
@@ -1276,17 +1276,17 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Results 2</t>
+          <t>Results 1</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Headline</t>
+          <t>Eyebrow</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Against the benchmark</t>
+          <t>Your position</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr"/>
@@ -1296,7 +1296,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Results 3</t>
+          <t>Results 2</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>And your role</t>
+          <t>Where you lead, where you lag</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr"/>
@@ -1316,17 +1316,17 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Results 3</t>
+          <t>Results 2</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Source note</t>
+          <t>Headline</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Matched from your badge · playbook workforce transformation table</t>
+          <t>Against the benchmark</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr"/>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>The human constraint</t>
+          <t>And your role</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr"/>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>Source note</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>The people most affected by AI are the domain experts who make it work. A team can have the model and still not trust it over decades of manual judgment, which is why the carriers that scale it own governance at board level and reward AI-enabled outcomes.</t>
+          <t>Matched from your badge · playbook workforce transformation table</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr"/>
@@ -1376,7 +1376,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Results 4</t>
+          <t>Results 3</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Five-year view</t>
+          <t>The human constraint</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr"/>
@@ -1396,17 +1396,17 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Results 4</t>
+          <t>Results 3</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Headline</t>
+          <t>Body</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Where the gap goes</t>
+          <t>The people most affected by AI are the domain experts who make it work. A team can have the model and still not trust it over decades of manual judgment, which is why the carriers that scale it own governance at board level and reward AI-enabled outcomes.</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr"/>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Lede</t>
+          <t>Eyebrow</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Unchanged, this is your five-year position.</t>
+          <t>Five-year view</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr"/>
@@ -1436,17 +1436,17 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Results 4</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Eyebrow</t>
+          <t>Headline</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Report dispatched</t>
+          <t>Where the gap goes</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr"/>
@@ -1456,17 +1456,17 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Results 4</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Headline</t>
+          <t>Lede</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>On its way</t>
+          <t>Unchanged, this is your five-year position.</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr"/>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>Eyebrow</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Sent to [email]. Three ways to get it back:</t>
+          <t>Report dispatched</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr"/>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Step 1</t>
+          <t>Headline</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Scan the code above</t>
+          <t>On its way</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr"/>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Step 2</t>
+          <t>Body</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Open the email we just sent</t>
+          <t>Sent to [email]. Three ways to get it back:</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr"/>
@@ -1541,17 +1541,57 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Step 3</t>
+          <t>Step 1</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Scan your badge at the booth to see and discuss your result</t>
+          <t>Scan the code above</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr"/>
       <c r="E42" s="8" t="inlineStr"/>
       <c r="F42" s="8" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Step 2</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Open the email we just sent</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr"/>
+      <c r="E43" s="8" t="inlineStr"/>
+      <c r="F43" s="8" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Scan your badge at the booth to see and discuss your result</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr"/>
+      <c r="E44" s="8" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Unlock AI Value - content for client review.xlsx
+++ b/Unlock AI Value - content for client review.xlsx
@@ -1604,17 +1604,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="42" customWidth="1" min="11" max="11"/>
@@ -1624,3594 +1624,1273 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>18 questions, 3 per pool, 5 answers each. Score drives the result: 4 = most mature, 0 = no capability. The question text appears once per group of five answers.</t>
+          <t>Six questions, one per value pool, each answered on a slider that snaps to five stops. Was 18 questions with five tap-options each; Anshul asked for fewer of both.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>If you change an answer, keep it to about three words, because the kiosk renders it at display size.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+          <t>The five stops run from least to most mature, left to right, scoring 0 / 25 / 50 / 75 / 100. Those five scores are exactly the five report bands, so every stop has its own report copy on the 'Score band feedback' sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Stop labels are the large text on the slider, so keep them to about three or four words. The detail line below updates as the visitor drags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Value pool</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Q ref</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Theme</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Free-text option?</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Answer (shown large)</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Answer detail (shown small)</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Stop label (shown large)</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Stop detail (shown small)</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>Approved? (Y/N)</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>Revised copy</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>Client comments</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Data for AI</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>DAT-1</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Unstructured documents</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>How do loss runs, treaties, medical files and adjuster notes reach your models?</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr"/>
-      <c r="F5" s="7" t="n">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Data readiness</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>How ready is your data for AI to actually use?</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Automated extraction pipeline</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Indexed, searchable, entity-linked at ingest</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Data for AI</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>DAT-1</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Unstructured documents</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>OCR plus manual review</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>Text extracted, humans still verify everything</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>3</v>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Not processed at all</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Policy, claims and treaty documents are never indexed</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
       <c r="L6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Data for AI</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>DAT-1</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Unstructured documents</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Staff transcribe manually</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Underwriters and adjusters retype into core</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="n">
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Data readiness</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr"/>
+      <c r="E7" s="9" t="inlineStr"/>
+      <c r="F7" s="9" t="n">
         <v>2</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Locked in PDFs</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Archived, but nothing can search or read them</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>25</v>
       </c>
       <c r="J7" s="8" t="inlineStr"/>
       <c r="K7" s="8" t="inlineStr"/>
       <c r="L7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Data for AI</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>DAT-1</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Unstructured documents</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr"/>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>Locked in PDFs</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>Archived but never indexed</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="n">
-        <v>1</v>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Data readiness</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>People retype it</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Underwriters and adjusters key documents into core systems</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>50</v>
       </c>
       <c r="J8" s="8" t="inlineStr"/>
       <c r="K8" s="8" t="inlineStr"/>
       <c r="L8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Data for AI</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>DAT-1</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Unstructured documents</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>No capability yet</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>Unstructured documents are not processed</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Data readiness</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr"/>
+      <c r="E9" s="9" t="inlineStr"/>
+      <c r="F9" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Extracted, humans verify</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Text is pulled out automatically, staff still check everything</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>75</v>
       </c>
       <c r="J9" s="8" t="inlineStr"/>
       <c r="K9" s="8" t="inlineStr"/>
       <c r="L9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Data for AI</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>DAT-2</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Cross-system retrieval</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>A model needs a policyholder’s full history across systems. How long does that take?</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>Real-time self-service</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>Unified data products served over APIs</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>4</v>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>DAT-1</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Data readiness</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Automated and audit-ready</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Indexed and entity-linked at ingest, with lineage a regulator can follow</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>100</v>
       </c>
       <c r="J10" s="8" t="inlineStr"/>
       <c r="K10" s="8" t="inlineStr"/>
       <c r="L10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Data for AI</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>DAT-2</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Cross-system retrieval</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>Days via ticket</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Request an extract and wait for batch</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>3</v>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>AI Strategy &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>STR-1</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Getting AI into production</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>How far has AI got beyond experiments in your business?</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Nothing in production</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>No AI model has gone live in core insurance</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="J11" s="8" t="inlineStr"/>
       <c r="K11" s="8" t="inlineStr"/>
       <c r="L11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Data for AI</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>DAT-2</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Cross-system retrieval</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr"/>
-      <c r="E12" s="9" t="inlineStr"/>
-      <c r="F12" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>Manual mainframe joins</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>Direct legacy queries stitched by hand</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="n">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>AI Strategy &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>STR-1</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Getting AI into production</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="7" t="n">
         <v>2</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>A few proofs of concept</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Pilots run, but nothing reaches production</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>25</v>
       </c>
       <c r="J12" s="8" t="inlineStr"/>
       <c r="K12" s="8" t="inlineStr"/>
       <c r="L12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Data for AI</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>DAT-2</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Cross-system retrieval</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Blocked by silos</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>Departmental boundaries prevent access</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>1</v>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>AI Strategy &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>STR-1</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Getting AI into production</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr"/>
+      <c r="E13" s="9" t="inlineStr"/>
+      <c r="F13" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Each business builds its own</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>Underwriting, claims and actuarial fund separately</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>50</v>
       </c>
       <c r="J13" s="8" t="inlineStr"/>
       <c r="K13" s="8" t="inlineStr"/>
       <c r="L13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Data for AI</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>DAT-2</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Cross-system retrieval</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr"/>
-      <c r="E14" s="9" t="inlineStr"/>
-      <c r="F14" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>Not currently possible</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>Cross-system integration does not exist</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="n">
-        <v>0</v>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>AI Strategy &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>STR-1</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Getting AI into production</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>One team funds the core</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>A digital function funds and governs central pilots</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>75</v>
       </c>
       <c r="J14" s="8" t="inlineStr"/>
       <c r="K14" s="8" t="inlineStr"/>
       <c r="L14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Data for AI</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>DAT-3</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Lineage &amp; audit trail</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Can you show a regulator exactly which data fed a given underwriting decision?</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Full automated lineage</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>Fingerprinted end to end, audit-ready</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="n">
-        <v>4</v>
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>AI Strategy &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>STR-1</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Getting AI into production</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>An enterprise AI factory</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>One governed roadmap and shared funding across every line</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>100</v>
       </c>
       <c r="J15" s="8" t="inlineStr"/>
       <c r="K15" s="8" t="inlineStr"/>
       <c r="L15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Data for AI</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>DAT-3</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Lineage &amp; audit trail</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr"/>
-      <c r="E16" s="9" t="inlineStr"/>
-      <c r="F16" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>Reconstructable with effort</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>Possible, but takes weeks of manual work</t>
-        </is>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>3</v>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>AI Trust</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>TRU-1</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Explaining an AI decision</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Could you explain an AI-driven decision to a regulator today?</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Nothing is documented and nothing is testable</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="J16" s="8" t="inlineStr"/>
       <c r="K16" s="8" t="inlineStr"/>
       <c r="L16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Data for AI</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>DAT-3</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Lineage &amp; audit trail</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr"/>
-      <c r="E17" s="7" t="inlineStr"/>
-      <c r="F17" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>Partial, system by system</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Some systems log it, others do not</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="n">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>AI Trust</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>TRU-1</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Explaining an AI decision</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr"/>
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="9" t="n">
         <v>2</v>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>Only after the fact</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>We could reconstruct it slowly, by hand</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>25</v>
       </c>
       <c r="J17" s="8" t="inlineStr"/>
       <c r="K17" s="8" t="inlineStr"/>
       <c r="L17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Data for AI</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>DAT-3</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Lineage &amp; audit trail</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr"/>
-      <c r="E18" s="9" t="inlineStr"/>
-      <c r="F18" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>Not reliably</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>We would struggle to evidence it</t>
-        </is>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>1</v>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>AI Trust</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>TRU-1</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Explaining an AI decision</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="7" t="inlineStr"/>
+      <c r="F18" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Checked at the end</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Bias and explainability are a final gate before release</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>50</v>
       </c>
       <c r="J18" s="8" t="inlineStr"/>
       <c r="K18" s="8" t="inlineStr"/>
       <c r="L18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Data for AI</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>DAT-3</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Lineage &amp; audit trail</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr"/>
-      <c r="E19" s="7" t="inlineStr"/>
-      <c r="F19" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>No lineage exists</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>No traceability at all</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>AI Trust</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>TRU-1</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Explaining an AI decision</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr"/>
+      <c r="E19" s="9" t="inlineStr"/>
+      <c r="F19" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>Built into the model</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>Explainability and bias testing sit in the architecture</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="n">
+        <v>75</v>
       </c>
       <c r="J19" s="8" t="inlineStr"/>
       <c r="K19" s="8" t="inlineStr"/>
       <c r="L19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>STR-1</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Funding &amp; prioritisation</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>How are AI initiatives funded and prioritised across your lines of business?</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr"/>
-      <c r="F20" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>Enterprise AI factory</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>One governed roadmap, shared funding across LOBs</t>
-        </is>
-      </c>
-      <c r="I20" s="9" t="n">
-        <v>4</v>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>AI Trust</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>TRU-1</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Explaining an AI decision</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr"/>
+      <c r="E20" s="7" t="inlineStr"/>
+      <c r="F20" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Ready on demand</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Audit trails and bias testing from the start, ready for NAIC and the EU AI Act</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>100</v>
       </c>
       <c r="J20" s="8" t="inlineStr"/>
       <c r="K20" s="8" t="inlineStr"/>
       <c r="L20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>STR-1</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Funding &amp; prioritisation</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
-      <c r="E21" s="7" t="inlineStr"/>
-      <c r="F21" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Central team funds</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>A digital function funds core pilots centrally</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="n">
-        <v>3</v>
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Physical AI</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>PHY-1</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Sensor and telematics data</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>What happens to the data from telematics, IoT and drones?</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>We do not collect it</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>No sensor or telematics feed exists</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="J21" s="8" t="inlineStr"/>
       <c r="K21" s="8" t="inlineStr"/>
       <c r="L21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>STR-1</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Funding &amp; prioritisation</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr"/>
-      <c r="E22" s="9" t="inlineStr"/>
-      <c r="F22" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>Each business separately</t>
-        </is>
-      </c>
-      <c r="H22" s="9" t="inlineStr">
-        <is>
-          <t>Underwriting, claims and actuarial buy their own</t>
-        </is>
-      </c>
-      <c r="I22" s="9" t="n">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Physical AI</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>PHY-1</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Sensor and telematics data</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr"/>
+      <c r="E22" s="7" t="inlineStr"/>
+      <c r="F22" s="7" t="n">
         <v>2</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Collected but unused</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>It lands somewhere and nothing reads it</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>25</v>
       </c>
       <c r="J22" s="8" t="inlineStr"/>
       <c r="K22" s="8" t="inlineStr"/>
       <c r="L22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>STR-1</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Funding &amp; prioritisation</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr"/>
-      <c r="E23" s="7" t="inlineStr"/>
-      <c r="F23" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>Opportunistic, case-by-case</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>Whoever has budget runs a proof of concept</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="n">
-        <v>1</v>
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Physical AI</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>PHY-1</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Sensor and telematics data</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr"/>
+      <c r="E23" s="9" t="inlineStr"/>
+      <c r="F23" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>A reporting by-product</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>It shows up in reports after the fact</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="n">
+        <v>50</v>
       </c>
       <c r="J23" s="8" t="inlineStr"/>
       <c r="K23" s="8" t="inlineStr"/>
       <c r="L23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>STR-1</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Funding &amp; prioritisation</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr"/>
-      <c r="E24" s="9" t="inlineStr"/>
-      <c r="F24" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>No formal process</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>No prioritisation mechanism exists</t>
-        </is>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>0</v>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Physical AI</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>PHY-1</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Sensor and telematics data</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr"/>
+      <c r="E24" s="7" t="inlineStr"/>
+      <c r="F24" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Feeds one price</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>One feed is engineered into pricing as a real input</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>75</v>
       </c>
       <c r="J24" s="8" t="inlineStr"/>
       <c r="K24" s="8" t="inlineStr"/>
       <c r="L24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>STR-2</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Path to production</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>What sits between an AI proof of concept and enterprise production?</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr"/>
-      <c r="F25" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>Shared engineering platform</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>Common platform with guardrails and reuse</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="n">
-        <v>4</v>
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Physical AI</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>PHY-1</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Sensor and telematics data</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr"/>
+      <c r="E25" s="9" t="inlineStr"/>
+      <c r="F25" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>A first-class input</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>Pricing and claims use it live, with digital twins for exposure</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="n">
+        <v>100</v>
       </c>
       <c r="J25" s="8" t="inlineStr"/>
       <c r="K25" s="8" t="inlineStr"/>
       <c r="L25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>STR-2</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Path to production</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr"/>
-      <c r="E26" s="9" t="inlineStr"/>
-      <c r="F26" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>Cloud services, custom pipelines</t>
-        </is>
-      </c>
-      <c r="H26" s="9" t="inlineStr">
-        <is>
-          <t>Standard services, but every LOB rebuilds</t>
-        </is>
-      </c>
-      <c r="I26" s="9" t="n">
-        <v>3</v>
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Agentic Legacy Modernization</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>LEG-1</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>The core platforms underneath</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>How are you handling the core platforms AI needs to reach?</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Frozen and untouchable</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Rating logic nobody fully understands, too risky to change</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="J26" s="8" t="inlineStr"/>
       <c r="K26" s="8" t="inlineStr"/>
       <c r="L26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>STR-2</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Path to production</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr"/>
-      <c r="E27" s="7" t="inlineStr"/>
-      <c r="F27" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>Fragmented vendor stacks</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>Manual glue code between disconnected tools</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="n">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Agentic Legacy Modernization</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>LEG-1</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>The core platforms underneath</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr"/>
+      <c r="E27" s="9" t="inlineStr"/>
+      <c r="F27" s="9" t="n">
         <v>2</v>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>Documented, not moving</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>The rules are written down but the platform is unchanged</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>25</v>
       </c>
       <c r="J27" s="8" t="inlineStr"/>
       <c r="K27" s="8" t="inlineStr"/>
       <c r="L27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>STR-2</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Path to production</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr"/>
-      <c r="E28" s="9" t="inlineStr"/>
-      <c r="F28" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>Bespoke every time</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="inlineStr">
-        <is>
-          <t>Each deployment is a fresh long build</t>
-        </is>
-      </c>
-      <c r="I28" s="9" t="n">
-        <v>1</v>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Agentic Legacy Modernization</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>LEG-1</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>The core platforms underneath</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr"/>
+      <c r="E28" s="7" t="inlineStr"/>
+      <c r="F28" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Rewriting by hand</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Modernisation is under way module by module, manually</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>50</v>
       </c>
       <c r="J28" s="8" t="inlineStr"/>
       <c r="K28" s="8" t="inlineStr"/>
       <c r="L28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>STR-2</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Path to production</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr"/>
-      <c r="E29" s="7" t="inlineStr"/>
-      <c r="F29" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>Nothing reaches production</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>No model has gone live in core insurance</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Agentic Legacy Modernization</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>LEG-1</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>The core platforms underneath</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr"/>
+      <c r="E29" s="9" t="inlineStr"/>
+      <c r="F29" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>AI recovers the intent</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>AI reads the legacy logic and rebuilds it as specification</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="n">
+        <v>75</v>
       </c>
       <c r="J29" s="8" t="inlineStr"/>
       <c r="K29" s="8" t="inlineStr"/>
       <c r="L29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>STR-3</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Inference cost governance</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>Who owns the token and inference cost of AI in production?</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>AI FinOps discipline</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>Cost modelled per workflow, routed by task</t>
-        </is>
-      </c>
-      <c r="I30" s="9" t="n">
-        <v>4</v>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Agentic Legacy Modernization</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>LEG-1</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>The core platforms underneath</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr"/>
+      <c r="E30" s="7" t="inlineStr"/>
+      <c r="F30" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Modernising while live</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>Module by module, with the book of business still trading</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>100</v>
       </c>
       <c r="J30" s="8" t="inlineStr"/>
       <c r="K30" s="8" t="inlineStr"/>
       <c r="L30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>STR-3</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Inference cost governance</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr"/>
-      <c r="E31" s="7" t="inlineStr"/>
-      <c r="F31" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>Tracked, not governed</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>Spend is visible but nobody optimises it</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="n">
-        <v>3</v>
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Process AI</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>PRO-1</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>How much of the journey AI runs</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>How much of a full claims or underwriting journey does AI run?</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>None of it</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>Core workflows are manual from end to end</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="J31" s="8" t="inlineStr"/>
       <c r="K31" s="8" t="inlineStr"/>
       <c r="L31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>STR-3</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Inference cost governance</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr"/>
-      <c r="E32" s="9" t="inlineStr"/>
-      <c r="F32" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>Visible at invoice</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="inlineStr">
-        <is>
-          <t>Discovered monthly when the bill arrives</t>
-        </is>
-      </c>
-      <c r="I32" s="9" t="n">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Process AI</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>PRO-1</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>How much of the journey AI runs</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr"/>
+      <c r="E32" s="7" t="inlineStr"/>
+      <c r="F32" s="7" t="n">
         <v>2</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>Isolated tasks</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>Automation sits inside a workflow nobody redesigned</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>25</v>
       </c>
       <c r="J32" s="8" t="inlineStr"/>
       <c r="K32" s="8" t="inlineStr"/>
       <c r="L32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>STR-3</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Inference cost governance</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr"/>
-      <c r="E33" s="7" t="inlineStr"/>
-      <c r="F33" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>Nobody tracks it</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>Unattributed and growing</t>
-        </is>
-      </c>
-      <c r="I33" s="7" t="n">
-        <v>1</v>
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Process AI</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>PRO-1</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>How much of the journey AI runs</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr"/>
+      <c r="E33" s="9" t="inlineStr"/>
+      <c r="F33" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>One journey rebuilt</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>A single journey has been mapped and rebuilt around AI</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="n">
+        <v>50</v>
       </c>
       <c r="J33" s="8" t="inlineStr"/>
       <c r="K33" s="8" t="inlineStr"/>
       <c r="L33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>STR-3</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Inference cost governance</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr"/>
-      <c r="E34" s="9" t="inlineStr"/>
-      <c r="F34" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>Not yet relevant</t>
-        </is>
-      </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t>Nothing at production scale yet</t>
-        </is>
-      </c>
-      <c r="I34" s="9" t="n">
-        <v>0</v>
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Process AI</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>PRO-1</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>How much of the journey AI runs</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr"/>
+      <c r="E34" s="7" t="inlineStr"/>
+      <c r="F34" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>Several journeys</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>Submission to bound, or FNOL to settlement, runs on agents</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>75</v>
       </c>
       <c r="J34" s="8" t="inlineStr"/>
       <c r="K34" s="8" t="inlineStr"/>
       <c r="L34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>AI Trust</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>TRU-1</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Regulatory readiness</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Could an AI underwriting decision survive an NAIC or EU AI Act review today?</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr"/>
-      <c r="F35" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>Governance by design</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>Multi-gate verification built into the lifecycle</t>
-        </is>
-      </c>
-      <c r="I35" s="7" t="n">
-        <v>4</v>
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Process AI</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>PRO-1</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>How much of the journey AI runs</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr"/>
+      <c r="E35" s="9" t="inlineStr"/>
+      <c r="F35" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>Agents alongside people</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>Whole journeys redesigned, with agents working next to underwriters</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="n">
+        <v>100</v>
       </c>
       <c r="J35" s="8" t="inlineStr"/>
       <c r="K35" s="8" t="inlineStr"/>
       <c r="L35" s="8" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>AI Trust</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>TRU-1</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Regulatory readiness</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr"/>
-      <c r="E36" s="9" t="inlineStr"/>
-      <c r="F36" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>Legal review, manual monitoring</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="inlineStr">
-        <is>
-          <t>Compliance sign-off, drift watched by hand</t>
-        </is>
-      </c>
-      <c r="I36" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J36" s="8" t="inlineStr"/>
-      <c r="K36" s="8" t="inlineStr"/>
-      <c r="L36" s="8" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>AI Trust</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>TRU-1</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Regulatory readiness</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr"/>
-      <c r="E37" s="7" t="inlineStr"/>
-      <c r="F37" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>Ad-hoc reviews only</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>Reviewed when someone remembers to ask</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J37" s="8" t="inlineStr"/>
-      <c r="K37" s="8" t="inlineStr"/>
-      <c r="L37" s="8" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>AI Trust</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>TRU-1</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Regulatory readiness</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr"/>
-      <c r="E38" s="9" t="inlineStr"/>
-      <c r="F38" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>Would not survive</t>
-        </is>
-      </c>
-      <c r="H38" s="9" t="inlineStr">
-        <is>
-          <t>We could not evidence the decision</t>
-        </is>
-      </c>
-      <c r="I38" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="8" t="inlineStr"/>
-      <c r="K38" s="8" t="inlineStr"/>
-      <c r="L38" s="8" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>AI Trust</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>TRU-1</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Regulatory readiness</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr"/>
-      <c r="E39" s="7" t="inlineStr"/>
-      <c r="F39" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>No AI in decisions</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>No models in regulated decisions yet</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="8" t="inlineStr"/>
-      <c r="K39" s="8" t="inlineStr"/>
-      <c r="L39" s="8" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>AI Trust</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>TRU-2</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>Bias &amp; fairness</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>When is fairness tested on a pricing or underwriting model?</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr"/>
-      <c r="F40" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>Before deployment, continuously</t>
-        </is>
-      </c>
-      <c r="H40" s="9" t="inlineStr">
-        <is>
-          <t>Tested in training and monitored after</t>
-        </is>
-      </c>
-      <c r="I40" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J40" s="8" t="inlineStr"/>
-      <c r="K40" s="8" t="inlineStr"/>
-      <c r="L40" s="8" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>AI Trust</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>TRU-2</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>Bias &amp; fairness</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr"/>
-      <c r="E41" s="7" t="inlineStr"/>
-      <c r="F41" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>At deployment only</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>Checked once, then left alone</t>
-        </is>
-      </c>
-      <c r="I41" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J41" s="8" t="inlineStr"/>
-      <c r="K41" s="8" t="inlineStr"/>
-      <c r="L41" s="8" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>AI Trust</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>TRU-2</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Bias &amp; fairness</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr"/>
-      <c r="E42" s="9" t="inlineStr"/>
-      <c r="F42" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G42" s="9" t="inlineStr">
-        <is>
-          <t>When challenged</t>
-        </is>
-      </c>
-      <c r="H42" s="9" t="inlineStr">
-        <is>
-          <t>Only after a complaint or query</t>
-        </is>
-      </c>
-      <c r="I42" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" s="8" t="inlineStr"/>
-      <c r="K42" s="8" t="inlineStr"/>
-      <c r="L42" s="8" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>AI Trust</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>TRU-2</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Bias &amp; fairness</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr"/>
-      <c r="E43" s="7" t="inlineStr"/>
-      <c r="F43" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>No fairness testing in place</t>
-        </is>
-      </c>
-      <c r="I43" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="8" t="inlineStr"/>
-      <c r="K43" s="8" t="inlineStr"/>
-      <c r="L43" s="8" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>AI Trust</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>TRU-2</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>Bias &amp; fairness</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="9" t="inlineStr"/>
-      <c r="F44" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G44" s="9" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="H44" s="9" t="inlineStr">
-        <is>
-          <t>No models affecting customers</t>
-        </is>
-      </c>
-      <c r="I44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="8" t="inlineStr"/>
-      <c r="K44" s="8" t="inlineStr"/>
-      <c r="L44" s="8" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>AI Trust</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>TRU-3</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>Explainability</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Can an underwriter trace the reasoning behind an AI risk score?</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>Full feature attribution</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>Scorecards generated for every decision</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J45" s="8" t="inlineStr"/>
-      <c r="K45" s="8" t="inlineStr"/>
-      <c r="L45" s="8" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>AI Trust</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>TRU-3</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>Explainability</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="inlineStr"/>
-      <c r="E46" s="9" t="inlineStr"/>
-      <c r="F46" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G46" s="9" t="inlineStr">
-        <is>
-          <t>Key inputs documented</t>
-        </is>
-      </c>
-      <c r="H46" s="9" t="inlineStr">
-        <is>
-          <t>Main drivers known, interactions opaque</t>
-        </is>
-      </c>
-      <c r="I46" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J46" s="8" t="inlineStr"/>
-      <c r="K46" s="8" t="inlineStr"/>
-      <c r="L46" s="8" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>AI Trust</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>TRU-3</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>Explainability</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr"/>
-      <c r="E47" s="7" t="inlineStr"/>
-      <c r="F47" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>Black-box vendor model</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>Limited visibility into vendor scoring</t>
-        </is>
-      </c>
-      <c r="I47" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J47" s="8" t="inlineStr"/>
-      <c r="K47" s="8" t="inlineStr"/>
-      <c r="L47" s="8" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>AI Trust</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>TRU-3</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>Explainability</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr"/>
-      <c r="E48" s="9" t="inlineStr"/>
-      <c r="F48" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G48" s="9" t="inlineStr">
-        <is>
-          <t>No explainability</t>
-        </is>
-      </c>
-      <c r="H48" s="9" t="inlineStr">
-        <is>
-          <t>Nothing available to underwriters or regulators</t>
-        </is>
-      </c>
-      <c r="I48" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="8" t="inlineStr"/>
-      <c r="K48" s="8" t="inlineStr"/>
-      <c r="L48" s="8" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>AI Trust</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>TRU-3</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>Explainability</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr"/>
-      <c r="E49" s="7" t="inlineStr"/>
-      <c r="F49" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>No AI risk scoring</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="8" t="inlineStr"/>
-      <c r="K49" s="8" t="inlineStr"/>
-      <c r="L49" s="8" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>Physical AI</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>PHY-1</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>Sensor ingestion</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>Does telematics and property IoT data reach your pricing models?</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="inlineStr"/>
-      <c r="F50" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="9" t="inlineStr">
-        <is>
-          <t>Streams into pricing</t>
-        </is>
-      </c>
-      <c r="H50" s="9" t="inlineStr">
-        <is>
-          <t>Continuous telemetry drives dynamic pricing</t>
-        </is>
-      </c>
-      <c r="I50" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J50" s="8" t="inlineStr"/>
-      <c r="K50" s="8" t="inlineStr"/>
-      <c r="L50" s="8" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>Physical AI</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>PHY-1</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>Sensor ingestion</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr"/>
-      <c r="E51" s="7" t="inlineStr"/>
-      <c r="F51" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>Auto telematics only</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>Motor uses it, commercial property in pilot</t>
-        </is>
-      </c>
-      <c r="I51" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J51" s="8" t="inlineStr"/>
-      <c r="K51" s="8" t="inlineStr"/>
-      <c r="L51" s="8" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>Physical AI</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>PHY-1</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>Sensor ingestion</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr"/>
-      <c r="E52" s="9" t="inlineStr"/>
-      <c r="F52" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>Pilots running</t>
-        </is>
-      </c>
-      <c r="H52" s="9" t="inlineStr">
-        <is>
-          <t>Small trials, nothing in production pricing</t>
-        </is>
-      </c>
-      <c r="I52" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" s="8" t="inlineStr"/>
-      <c r="K52" s="8" t="inlineStr"/>
-      <c r="L52" s="8" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>Physical AI</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>PHY-1</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>Sensor ingestion</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr"/>
-      <c r="E53" s="7" t="inlineStr"/>
-      <c r="F53" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>Collected, unused</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>Data arrives but never reaches a model</t>
-        </is>
-      </c>
-      <c r="I53" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="8" t="inlineStr"/>
-      <c r="K53" s="8" t="inlineStr"/>
-      <c r="L53" s="8" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>Physical AI</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>PHY-1</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>Sensor ingestion</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr"/>
-      <c r="E54" s="9" t="inlineStr"/>
-      <c r="F54" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t>No sensor data</t>
-        </is>
-      </c>
-      <c r="H54" s="9" t="inlineStr">
-        <is>
-          <t>No ingestion of physical signals</t>
-        </is>
-      </c>
-      <c r="I54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="8" t="inlineStr"/>
-      <c r="K54" s="8" t="inlineStr"/>
-      <c r="L54" s="8" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>Physical AI</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>PHY-2</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>Claims inspection</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>How is physical damage assessed after a loss event?</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr"/>
-      <c r="F55" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>Drone and vision assessment</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>Imagery scored automatically within hours</t>
-        </is>
-      </c>
-      <c r="I55" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J55" s="8" t="inlineStr"/>
-      <c r="K55" s="8" t="inlineStr"/>
-      <c r="L55" s="8" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>Physical AI</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>PHY-2</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>Claims inspection</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="inlineStr"/>
-      <c r="E56" s="9" t="inlineStr"/>
-      <c r="F56" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>Mobile app pilot</t>
-        </is>
-      </c>
-      <c r="H56" s="9" t="inlineStr">
-        <is>
-          <t>Policyholder photo capture being trialled</t>
-        </is>
-      </c>
-      <c r="I56" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J56" s="8" t="inlineStr"/>
-      <c r="K56" s="8" t="inlineStr"/>
-      <c r="L56" s="8" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>Physical AI</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>PHY-2</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>Claims inspection</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr"/>
-      <c r="E57" s="7" t="inlineStr"/>
-      <c r="F57" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>Photos, manual review</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>Images uploaded for an adjuster to read</t>
-        </is>
-      </c>
-      <c r="I57" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J57" s="8" t="inlineStr"/>
-      <c r="K57" s="8" t="inlineStr"/>
-      <c r="L57" s="8" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="inlineStr">
-        <is>
-          <t>Physical AI</t>
-        </is>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>PHY-2</t>
-        </is>
-      </c>
-      <c r="C58" s="9" t="inlineStr">
-        <is>
-          <t>Claims inspection</t>
-        </is>
-      </c>
-      <c r="D58" s="9" t="inlineStr"/>
-      <c r="E58" s="9" t="inlineStr"/>
-      <c r="F58" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G58" s="9" t="inlineStr">
-        <is>
-          <t>Physical inspection only</t>
-        </is>
-      </c>
-      <c r="H58" s="9" t="inlineStr">
-        <is>
-          <t>Someone has to attend the site</t>
-        </is>
-      </c>
-      <c r="I58" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="8" t="inlineStr"/>
-      <c r="K58" s="8" t="inlineStr"/>
-      <c r="L58" s="8" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>Physical AI</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>PHY-2</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>Claims inspection</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr"/>
-      <c r="E59" s="7" t="inlineStr"/>
-      <c r="F59" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>No physical damage in our book</t>
-        </is>
-      </c>
-      <c r="I59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="8" t="inlineStr"/>
-      <c r="K59" s="8" t="inlineStr"/>
-      <c r="L59" s="8" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>Physical AI</t>
-        </is>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>PHY-3</t>
-        </is>
-      </c>
-      <c r="C60" s="9" t="inlineStr">
-        <is>
-          <t>Digital twins</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>Can you simulate exposure on an insured asset before a loss occurs?</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F60" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>Digital twins live</t>
-        </is>
-      </c>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>Loss scenarios modelled on live asset data</t>
-        </is>
-      </c>
-      <c r="I60" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J60" s="8" t="inlineStr"/>
-      <c r="K60" s="8" t="inlineStr"/>
-      <c r="L60" s="8" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>Physical AI</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>PHY-3</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>Digital twins</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr"/>
-      <c r="E61" s="7" t="inlineStr"/>
-      <c r="F61" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>Modelling in pilot</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>Twin concepts being tested on a segment</t>
-        </is>
-      </c>
-      <c r="I61" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J61" s="8" t="inlineStr"/>
-      <c r="K61" s="8" t="inlineStr"/>
-      <c r="L61" s="8" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="9" t="inlineStr">
-        <is>
-          <t>Physical AI</t>
-        </is>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>PHY-3</t>
-        </is>
-      </c>
-      <c r="C62" s="9" t="inlineStr">
-        <is>
-          <t>Digital twins</t>
-        </is>
-      </c>
-      <c r="D62" s="9" t="inlineStr"/>
-      <c r="E62" s="9" t="inlineStr"/>
-      <c r="F62" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G62" s="9" t="inlineStr">
-        <is>
-          <t>Static exposure models</t>
-        </is>
-      </c>
-      <c r="H62" s="9" t="inlineStr">
-        <is>
-          <t>Periodic actuarial modelling only</t>
-        </is>
-      </c>
-      <c r="I62" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J62" s="8" t="inlineStr"/>
-      <c r="K62" s="8" t="inlineStr"/>
-      <c r="L62" s="8" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>Physical AI</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>PHY-3</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>Digital twins</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr"/>
-      <c r="E63" s="7" t="inlineStr"/>
-      <c r="F63" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>Post-loss analysis</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>We only look after the claim</t>
-        </is>
-      </c>
-      <c r="I63" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="8" t="inlineStr"/>
-      <c r="K63" s="8" t="inlineStr"/>
-      <c r="L63" s="8" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="9" t="inlineStr">
-        <is>
-          <t>Physical AI</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>PHY-3</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="inlineStr">
-        <is>
-          <t>Digital twins</t>
-        </is>
-      </c>
-      <c r="D64" s="9" t="inlineStr"/>
-      <c r="E64" s="9" t="inlineStr"/>
-      <c r="F64" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G64" s="9" t="inlineStr">
-        <is>
-          <t>No capability</t>
-        </is>
-      </c>
-      <c r="H64" s="9" t="inlineStr">
-        <is>
-          <t>Not modelled</t>
-        </is>
-      </c>
-      <c r="I64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="8" t="inlineStr"/>
-      <c r="K64" s="8" t="inlineStr"/>
-      <c r="L64" s="8" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>Agentic Legacy Modernization</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>LEG-1</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>Core platform drag</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>How much does your core policy platform slow a new product launch?</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr"/>
-      <c r="F65" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="7" t="inlineStr">
-        <is>
-          <t>Weeks, not months</t>
-        </is>
-      </c>
-      <c r="H65" s="7" t="inlineStr">
-        <is>
-          <t>Logic exposed as APIs, launches are routine</t>
-        </is>
-      </c>
-      <c r="I65" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J65" s="8" t="inlineStr"/>
-      <c r="K65" s="8" t="inlineStr"/>
-      <c r="L65" s="8" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="9" t="inlineStr">
-        <is>
-          <t>Agentic Legacy Modernization</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>LEG-1</t>
-        </is>
-      </c>
-      <c r="C66" s="9" t="inlineStr">
-        <is>
-          <t>Core platform drag</t>
-        </is>
-      </c>
-      <c r="D66" s="9" t="inlineStr"/>
-      <c r="E66" s="9" t="inlineStr"/>
-      <c r="F66" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G66" s="9" t="inlineStr">
-        <is>
-          <t>Wrappers, fragile core</t>
-        </is>
-      </c>
-      <c r="H66" s="9" t="inlineStr">
-        <is>
-          <t>Modern APIs over brittle rating algorithms</t>
-        </is>
-      </c>
-      <c r="I66" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J66" s="8" t="inlineStr"/>
-      <c r="K66" s="8" t="inlineStr"/>
-      <c r="L66" s="8" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>Agentic Legacy Modernization</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>LEG-1</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>Core platform drag</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr"/>
-      <c r="E67" s="7" t="inlineStr"/>
-      <c r="F67" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>Twelve months plus</t>
-        </is>
-      </c>
-      <c r="H67" s="7" t="inlineStr">
-        <is>
-          <t>Technical debt sets the pace of the roadmap</t>
-        </is>
-      </c>
-      <c r="I67" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J67" s="8" t="inlineStr"/>
-      <c r="K67" s="8" t="inlineStr"/>
-      <c r="L67" s="8" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="9" t="inlineStr">
-        <is>
-          <t>Agentic Legacy Modernization</t>
-        </is>
-      </c>
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t>LEG-1</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>Core platform drag</t>
-        </is>
-      </c>
-      <c r="D68" s="9" t="inlineStr"/>
-      <c r="E68" s="9" t="inlineStr"/>
-      <c r="F68" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G68" s="9" t="inlineStr">
-        <is>
-          <t>Leadership avoids touching</t>
-        </is>
-      </c>
-      <c r="H68" s="9" t="inlineStr">
-        <is>
-          <t>Change is considered too risky to attempt</t>
-        </is>
-      </c>
-      <c r="I68" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="8" t="inlineStr"/>
-      <c r="K68" s="8" t="inlineStr"/>
-      <c r="L68" s="8" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t>Agentic Legacy Modernization</t>
-        </is>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>LEG-1</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>Core platform drag</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr"/>
-      <c r="E69" s="7" t="inlineStr"/>
-      <c r="F69" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G69" s="7" t="inlineStr">
-        <is>
-          <t>No audit exists</t>
-        </is>
-      </c>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>We have not mapped the estate at all</t>
-        </is>
-      </c>
-      <c r="I69" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="8" t="inlineStr"/>
-      <c r="K69" s="8" t="inlineStr"/>
-      <c r="L69" s="8" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="9" t="inlineStr">
-        <is>
-          <t>Agentic Legacy Modernization</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>LEG-2</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>Embedded business logic</t>
-        </is>
-      </c>
-      <c r="D70" s="9" t="inlineStr">
-        <is>
-          <t>How well is your rating, filing and exception logic documented?</t>
-        </is>
-      </c>
-      <c r="E70" s="9" t="inlineStr"/>
-      <c r="F70" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" s="9" t="inlineStr">
-        <is>
-          <t>AI-mapped, machine readable</t>
-        </is>
-      </c>
-      <c r="H70" s="9" t="inlineStr">
-        <is>
-          <t>Rules and schemas extracted automatically</t>
-        </is>
-      </c>
-      <c r="I70" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J70" s="8" t="inlineStr"/>
-      <c r="K70" s="8" t="inlineStr"/>
-      <c r="L70" s="8" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t>Agentic Legacy Modernization</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>LEG-2</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>Embedded business logic</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr"/>
-      <c r="E71" s="7" t="inlineStr"/>
-      <c r="F71" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>Partial, seniors know</t>
-        </is>
-      </c>
-      <c r="H71" s="7" t="inlineStr">
-        <is>
-          <t>Some documentation, rest is institutional memory</t>
-        </is>
-      </c>
-      <c r="I71" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J71" s="8" t="inlineStr"/>
-      <c r="K71" s="8" t="inlineStr"/>
-      <c r="L71" s="8" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="9" t="inlineStr">
-        <is>
-          <t>Agentic Legacy Modernization</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>LEG-2</t>
-        </is>
-      </c>
-      <c r="C72" s="9" t="inlineStr">
-        <is>
-          <t>Embedded business logic</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="inlineStr"/>
-      <c r="E72" s="9" t="inlineStr"/>
-      <c r="F72" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G72" s="9" t="inlineStr">
-        <is>
-          <t>Few veterans remaining</t>
-        </is>
-      </c>
-      <c r="H72" s="9" t="inlineStr">
-        <is>
-          <t>Knowledge sits with people close to retirement</t>
-        </is>
-      </c>
-      <c r="I72" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" s="8" t="inlineStr"/>
-      <c r="K72" s="8" t="inlineStr"/>
-      <c r="L72" s="8" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t>Agentic Legacy Modernization</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>LEG-2</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>Embedded business logic</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr"/>
-      <c r="E73" s="7" t="inlineStr"/>
-      <c r="F73" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G73" s="7" t="inlineStr">
-        <is>
-          <t>Undocumented black box</t>
-        </is>
-      </c>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>Must be reverse-engineered line by line</t>
-        </is>
-      </c>
-      <c r="I73" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="8" t="inlineStr"/>
-      <c r="K73" s="8" t="inlineStr"/>
-      <c r="L73" s="8" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="9" t="inlineStr">
-        <is>
-          <t>Agentic Legacy Modernization</t>
-        </is>
-      </c>
-      <c r="B74" s="9" t="inlineStr">
-        <is>
-          <t>LEG-2</t>
-        </is>
-      </c>
-      <c r="C74" s="9" t="inlineStr">
-        <is>
-          <t>Embedded business logic</t>
-        </is>
-      </c>
-      <c r="D74" s="9" t="inlineStr"/>
-      <c r="E74" s="9" t="inlineStr"/>
-      <c r="F74" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G74" s="9" t="inlineStr">
-        <is>
-          <t>Nobody knows</t>
-        </is>
-      </c>
-      <c r="H74" s="9" t="inlineStr">
-        <is>
-          <t>The logic is effectively lost</t>
-        </is>
-      </c>
-      <c r="I74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="8" t="inlineStr"/>
-      <c r="K74" s="8" t="inlineStr"/>
-      <c r="L74" s="8" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>Agentic Legacy Modernization</t>
-        </is>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>LEG-3</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>Modernisation route</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>What is your modernisation route?</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F75" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="7" t="inlineStr">
-        <is>
-          <t>Progressive, validated increments</t>
-        </is>
-      </c>
-      <c r="H75" s="7" t="inlineStr">
-        <is>
-          <t>Module by module, verified against legacy</t>
-        </is>
-      </c>
-      <c r="I75" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J75" s="8" t="inlineStr"/>
-      <c r="K75" s="8" t="inlineStr"/>
-      <c r="L75" s="8" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="9" t="inlineStr">
-        <is>
-          <t>Agentic Legacy Modernization</t>
-        </is>
-      </c>
-      <c r="B76" s="9" t="inlineStr">
-        <is>
-          <t>LEG-3</t>
-        </is>
-      </c>
-      <c r="C76" s="9" t="inlineStr">
-        <is>
-          <t>Modernisation route</t>
-        </is>
-      </c>
-      <c r="D76" s="9" t="inlineStr"/>
-      <c r="E76" s="9" t="inlineStr"/>
-      <c r="F76" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G76" s="9" t="inlineStr">
-        <is>
-          <t>Phased by module</t>
-        </is>
-      </c>
-      <c r="H76" s="9" t="inlineStr">
-        <is>
-          <t>Sequenced plan, partially underway</t>
-        </is>
-      </c>
-      <c r="I76" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J76" s="8" t="inlineStr"/>
-      <c r="K76" s="8" t="inlineStr"/>
-      <c r="L76" s="8" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>Agentic Legacy Modernization</t>
-        </is>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>LEG-3</t>
-        </is>
-      </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>Modernisation route</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr"/>
-      <c r="E77" s="7" t="inlineStr"/>
-      <c r="F77" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G77" s="7" t="inlineStr">
-        <is>
-          <t>Big-bang replacement</t>
-        </is>
-      </c>
-      <c r="H77" s="7" t="inlineStr">
-        <is>
-          <t>One large cutover programme planned</t>
-        </is>
-      </c>
-      <c r="I77" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J77" s="8" t="inlineStr"/>
-      <c r="K77" s="8" t="inlineStr"/>
-      <c r="L77" s="8" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="9" t="inlineStr">
-        <is>
-          <t>Agentic Legacy Modernization</t>
-        </is>
-      </c>
-      <c r="B78" s="9" t="inlineStr">
-        <is>
-          <t>LEG-3</t>
-        </is>
-      </c>
-      <c r="C78" s="9" t="inlineStr">
-        <is>
-          <t>Modernisation route</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="inlineStr"/>
-      <c r="E78" s="9" t="inlineStr"/>
-      <c r="F78" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G78" s="9" t="inlineStr">
-        <is>
-          <t>Stalled business case</t>
-        </is>
-      </c>
-      <c r="H78" s="9" t="inlineStr">
-        <is>
-          <t>Approved in principle, never funded</t>
-        </is>
-      </c>
-      <c r="I78" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="8" t="inlineStr"/>
-      <c r="K78" s="8" t="inlineStr"/>
-      <c r="L78" s="8" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>Agentic Legacy Modernization</t>
-        </is>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>LEG-3</t>
-        </is>
-      </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>Modernisation route</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr"/>
-      <c r="E79" s="7" t="inlineStr"/>
-      <c r="F79" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G79" s="7" t="inlineStr">
-        <is>
-          <t>No plan</t>
-        </is>
-      </c>
-      <c r="H79" s="7" t="inlineStr">
-        <is>
-          <t>Nothing scoped</t>
-        </is>
-      </c>
-      <c r="I79" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="8" t="inlineStr"/>
-      <c r="K79" s="8" t="inlineStr"/>
-      <c r="L79" s="8" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
-        <is>
-          <t>Process AI</t>
-        </is>
-      </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>PRO-1</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>Pre-bind submission</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr">
-        <is>
-          <t>How much of pre-bind submission qualification happens without a human?</t>
-        </is>
-      </c>
-      <c r="E80" s="9" t="inlineStr"/>
-      <c r="F80" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="9" t="inlineStr">
-        <is>
-          <t>Autonomous triage, auto-decline</t>
-        </is>
-      </c>
-      <c r="H80" s="9" t="inlineStr">
-        <is>
-          <t>Out-of-appetite risks declined before the desk</t>
-        </is>
-      </c>
-      <c r="I80" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J80" s="8" t="inlineStr"/>
-      <c r="K80" s="8" t="inlineStr"/>
-      <c r="L80" s="8" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>Process AI</t>
-        </is>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>PRO-1</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t>Pre-bind submission</t>
-        </is>
-      </c>
-      <c r="D81" s="7" t="inlineStr"/>
-      <c r="E81" s="7" t="inlineStr"/>
-      <c r="F81" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G81" s="7" t="inlineStr">
-        <is>
-          <t>AI summarises, human qualifies</t>
-        </is>
-      </c>
-      <c r="H81" s="7" t="inlineStr">
-        <is>
-          <t>Assisted reading, manual decision</t>
-        </is>
-      </c>
-      <c r="I81" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J81" s="8" t="inlineStr"/>
-      <c r="K81" s="8" t="inlineStr"/>
-      <c r="L81" s="8" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>Process AI</t>
-        </is>
-      </c>
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t>PRO-1</t>
-        </is>
-      </c>
-      <c r="C82" s="9" t="inlineStr">
-        <is>
-          <t>Pre-bind submission</t>
-        </is>
-      </c>
-      <c r="D82" s="9" t="inlineStr"/>
-      <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>RPA handles entry</t>
-        </is>
-      </c>
-      <c r="H82" s="9" t="inlineStr">
-        <is>
-          <t>Scripts move data, people still qualify</t>
-        </is>
-      </c>
-      <c r="I82" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="8" t="inlineStr"/>
-      <c r="K82" s="8" t="inlineStr"/>
-      <c r="L82" s="8" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="7" t="inlineStr">
-        <is>
-          <t>Process AI</t>
-        </is>
-      </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>PRO-1</t>
-        </is>
-      </c>
-      <c r="C83" s="7" t="inlineStr">
-        <is>
-          <t>Pre-bind submission</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="inlineStr"/>
-      <c r="E83" s="7" t="inlineStr"/>
-      <c r="F83" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G83" s="7" t="inlineStr">
-        <is>
-          <t>Hours per submission</t>
-        </is>
-      </c>
-      <c r="H83" s="7" t="inlineStr">
-        <is>
-          <t>One to two hours just to assess completeness</t>
-        </is>
-      </c>
-      <c r="I83" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="8" t="inlineStr"/>
-      <c r="K83" s="8" t="inlineStr"/>
-      <c r="L83" s="8" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="9" t="inlineStr">
-        <is>
-          <t>Process AI</t>
-        </is>
-      </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>PRO-1</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>Pre-bind submission</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr"/>
-      <c r="E84" s="9" t="inlineStr"/>
-      <c r="F84" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G84" s="9" t="inlineStr">
-        <is>
-          <t>Entirely manual intake</t>
-        </is>
-      </c>
-      <c r="H84" s="9" t="inlineStr">
-        <is>
-          <t>No digital assistance at all</t>
-        </is>
-      </c>
-      <c r="I84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="8" t="inlineStr"/>
-      <c r="K84" s="8" t="inlineStr"/>
-      <c r="L84" s="8" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="7" t="inlineStr">
-        <is>
-          <t>Process AI</t>
-        </is>
-      </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>PRO-2</t>
-        </is>
-      </c>
-      <c r="C85" s="7" t="inlineStr">
-        <is>
-          <t>FNOL to settlement</t>
-        </is>
-      </c>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>How touchless is First Notice of Loss through to settlement on routine claims?</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="inlineStr"/>
-      <c r="F85" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="7" t="inlineStr">
-        <is>
-          <t>Straight-through settlement</t>
-        </is>
-      </c>
-      <c r="H85" s="7" t="inlineStr">
-        <is>
-          <t>Coverage verified and routine claims settled</t>
-        </is>
-      </c>
-      <c r="I85" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J85" s="8" t="inlineStr"/>
-      <c r="K85" s="8" t="inlineStr"/>
-      <c r="L85" s="8" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="9" t="inlineStr">
-        <is>
-          <t>Process AI</t>
-        </is>
-      </c>
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t>PRO-2</t>
-        </is>
-      </c>
-      <c r="C86" s="9" t="inlineStr">
-        <is>
-          <t>FNOL to settlement</t>
-        </is>
-      </c>
-      <c r="D86" s="9" t="inlineStr"/>
-      <c r="E86" s="9" t="inlineStr"/>
-      <c r="F86" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G86" s="9" t="inlineStr">
-        <is>
-          <t>AI triage, human decides</t>
-        </is>
-      </c>
-      <c r="H86" s="9" t="inlineStr">
-        <is>
-          <t>Severity scored, reserves recommended</t>
-        </is>
-      </c>
-      <c r="I86" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J86" s="8" t="inlineStr"/>
-      <c r="K86" s="8" t="inlineStr"/>
-      <c r="L86" s="8" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="7" t="inlineStr">
-        <is>
-          <t>Process AI</t>
-        </is>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>PRO-2</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>FNOL to settlement</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="inlineStr"/>
-      <c r="E87" s="7" t="inlineStr"/>
-      <c r="F87" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G87" s="7" t="inlineStr">
-        <is>
-          <t>Digital intake, manual adjudication</t>
-        </is>
-      </c>
-      <c r="H87" s="7" t="inlineStr">
-        <is>
-          <t>Web forms front a manual process</t>
-        </is>
-      </c>
-      <c r="I87" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J87" s="8" t="inlineStr"/>
-      <c r="K87" s="8" t="inlineStr"/>
-      <c r="L87" s="8" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="9" t="inlineStr">
-        <is>
-          <t>Process AI</t>
-        </is>
-      </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>PRO-2</t>
-        </is>
-      </c>
-      <c r="C88" s="9" t="inlineStr">
-        <is>
-          <t>FNOL to settlement</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="inlineStr"/>
-      <c r="E88" s="9" t="inlineStr"/>
-      <c r="F88" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G88" s="9" t="inlineStr">
-        <is>
-          <t>Manual across systems</t>
-        </is>
-      </c>
-      <c r="H88" s="9" t="inlineStr">
-        <is>
-          <t>Adjusters work step by step, system to system</t>
-        </is>
-      </c>
-      <c r="I88" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="8" t="inlineStr"/>
-      <c r="K88" s="8" t="inlineStr"/>
-      <c r="L88" s="8" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>Process AI</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>PRO-2</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>FNOL to settlement</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr"/>
-      <c r="E89" s="7" t="inlineStr"/>
-      <c r="F89" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>Paper-based process</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>Physical files and manual handoffs</t>
-        </is>
-      </c>
-      <c r="I89" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="8" t="inlineStr"/>
-      <c r="K89" s="8" t="inlineStr"/>
-      <c r="L89" s="8" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="9" t="inlineStr">
-        <is>
-          <t>Process AI</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="inlineStr">
-        <is>
-          <t>PRO-3</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="inlineStr">
-        <is>
-          <t>Workflow redesign</t>
-        </is>
-      </c>
-      <c r="D90" s="9" t="inlineStr">
-        <is>
-          <t>Was the workflow redesigned around AI, or was AI added to the existing one?</t>
-        </is>
-      </c>
-      <c r="E90" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F90" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" s="9" t="inlineStr">
-        <is>
-          <t>End-to-end redesign</t>
-        </is>
-      </c>
-      <c r="H90" s="9" t="inlineStr">
-        <is>
-          <t>The whole journey was rebuilt around agents</t>
-        </is>
-      </c>
-      <c r="I90" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J90" s="8" t="inlineStr"/>
-      <c r="K90" s="8" t="inlineStr"/>
-      <c r="L90" s="8" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="7" t="inlineStr">
-        <is>
-          <t>Process AI</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>PRO-3</t>
-        </is>
-      </c>
-      <c r="C91" s="7" t="inlineStr">
-        <is>
-          <t>Workflow redesign</t>
-        </is>
-      </c>
-      <c r="D91" s="7" t="inlineStr"/>
-      <c r="E91" s="7" t="inlineStr"/>
-      <c r="F91" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G91" s="7" t="inlineStr">
-        <is>
-          <t>Redesigned in places</t>
-        </is>
-      </c>
-      <c r="H91" s="7" t="inlineStr">
-        <is>
-          <t>Some journeys reworked, others untouched</t>
-        </is>
-      </c>
-      <c r="I91" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J91" s="8" t="inlineStr"/>
-      <c r="K91" s="8" t="inlineStr"/>
-      <c r="L91" s="8" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="9" t="inlineStr">
-        <is>
-          <t>Process AI</t>
-        </is>
-      </c>
-      <c r="B92" s="9" t="inlineStr">
-        <is>
-          <t>PRO-3</t>
-        </is>
-      </c>
-      <c r="C92" s="9" t="inlineStr">
-        <is>
-          <t>Workflow redesign</t>
-        </is>
-      </c>
-      <c r="D92" s="9" t="inlineStr"/>
-      <c r="E92" s="9" t="inlineStr"/>
-      <c r="F92" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G92" s="9" t="inlineStr">
-        <is>
-          <t>AI bolted on</t>
-        </is>
-      </c>
-      <c r="H92" s="9" t="inlineStr">
-        <is>
-          <t>Same process, one step now assisted</t>
-        </is>
-      </c>
-      <c r="I92" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J92" s="8" t="inlineStr"/>
-      <c r="K92" s="8" t="inlineStr"/>
-      <c r="L92" s="8" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="7" t="inlineStr">
-        <is>
-          <t>Process AI</t>
-        </is>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>PRO-3</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="inlineStr">
-        <is>
-          <t>Workflow redesign</t>
-        </is>
-      </c>
-      <c r="D93" s="7" t="inlineStr"/>
-      <c r="E93" s="7" t="inlineStr"/>
-      <c r="F93" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G93" s="7" t="inlineStr">
-        <is>
-          <t>Task automation only</t>
-        </is>
-      </c>
-      <c r="H93" s="7" t="inlineStr">
-        <is>
-          <t>Individual tasks automated in isolation</t>
-        </is>
-      </c>
-      <c r="I93" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" s="8" t="inlineStr"/>
-      <c r="K93" s="8" t="inlineStr"/>
-      <c r="L93" s="8" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="9" t="inlineStr">
-        <is>
-          <t>Process AI</t>
-        </is>
-      </c>
-      <c r="B94" s="9" t="inlineStr">
-        <is>
-          <t>PRO-3</t>
-        </is>
-      </c>
-      <c r="C94" s="9" t="inlineStr">
-        <is>
-          <t>Workflow redesign</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="inlineStr"/>
-      <c r="E94" s="9" t="inlineStr"/>
-      <c r="F94" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G94" s="9" t="inlineStr">
-        <is>
-          <t>No change yet</t>
-        </is>
-      </c>
-      <c r="H94" s="9" t="inlineStr">
-        <is>
-          <t>Process is unchanged</t>
-        </is>
-      </c>
-      <c r="I94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="8" t="inlineStr"/>
-      <c r="K94" s="8" t="inlineStr"/>
-      <c r="L94" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7803,10 +5482,10 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="D5" s="10" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr"/>
@@ -7822,10 +5501,10 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="D6" s="10" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr"/>
@@ -7841,10 +5520,10 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="D7" s="10" t="inlineStr"/>
       <c r="E7" s="8" t="inlineStr"/>
@@ -7860,10 +5539,10 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
       <c r="E8" s="8" t="inlineStr"/>
@@ -7879,10 +5558,10 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
       <c r="E9" s="8" t="inlineStr"/>
@@ -7898,10 +5577,10 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
       <c r="E10" s="8" t="inlineStr"/>

--- a/Unlock AI Value - content for client review.xlsx
+++ b/Unlock AI Value - content for client review.xlsx
@@ -1604,21 +1604,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="52" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="42" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1665,40 +1664,35 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Free-text option?</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Stop label (shown large)</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Stop label (shown large)</t>
+          <t>Stop detail (shown small)</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Stop detail (shown small)</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Approved? (Y/N)</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Approved? (Y/N)</t>
+          <t>Revised copy</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>Revised copy</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>Client comments</t>
         </is>
@@ -1725,30 +1719,25 @@
           <t>How ready is your data for AI to actually use?</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="n">
+      <c r="E6" s="7" t="n">
         <v>1</v>
       </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Not processed at all</t>
+        </is>
+      </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Not processed at all</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
           <t>Policy, claims and treaty documents are never indexed</t>
         </is>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="H6" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -1767,26 +1756,25 @@
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr"/>
-      <c r="E7" s="9" t="inlineStr"/>
-      <c r="F7" s="9" t="n">
+      <c r="E7" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Locked in PDFs</t>
+        </is>
+      </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Locked in PDFs</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
           <t>Archived, but nothing can search or read them</t>
         </is>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="H7" s="9" t="n">
         <v>25</v>
       </c>
+      <c r="I7" s="8" t="inlineStr"/>
       <c r="J7" s="8" t="inlineStr"/>
       <c r="K7" s="8" t="inlineStr"/>
-      <c r="L7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -1805,26 +1793,25 @@
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr"/>
-      <c r="F8" s="7" t="n">
+      <c r="E8" s="7" t="n">
         <v>3</v>
       </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>People retype it</t>
+        </is>
+      </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>People retype it</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
           <t>Underwriters and adjusters key documents into core systems</t>
         </is>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="H8" s="7" t="n">
         <v>50</v>
       </c>
+      <c r="I8" s="8" t="inlineStr"/>
       <c r="J8" s="8" t="inlineStr"/>
       <c r="K8" s="8" t="inlineStr"/>
-      <c r="L8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -1843,26 +1830,25 @@
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr"/>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="9" t="n">
+      <c r="E9" s="9" t="n">
         <v>4</v>
       </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Extracted, humans verify</t>
+        </is>
+      </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>Extracted, humans verify</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
           <t>Text is pulled out automatically, staff still check everything</t>
         </is>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="H9" s="9" t="n">
         <v>75</v>
       </c>
+      <c r="I9" s="8" t="inlineStr"/>
       <c r="J9" s="8" t="inlineStr"/>
       <c r="K9" s="8" t="inlineStr"/>
-      <c r="L9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -1881,26 +1867,25 @@
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="n">
+      <c r="E10" s="7" t="n">
         <v>5</v>
       </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Automated and audit-ready</t>
+        </is>
+      </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Automated and audit-ready</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
           <t>Indexed and entity-linked at ingest, with lineage a regulator can follow</t>
         </is>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="H10" s="7" t="n">
         <v>100</v>
       </c>
+      <c r="I10" s="8" t="inlineStr"/>
       <c r="J10" s="8" t="inlineStr"/>
       <c r="K10" s="8" t="inlineStr"/>
-      <c r="L10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -1923,30 +1908,25 @@
           <t>How far has AI got beyond experiments in your business?</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="n">
+      <c r="E11" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Nothing in production</t>
+        </is>
+      </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Nothing in production</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
           <t>No AI model has gone live in core insurance</t>
         </is>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="H11" s="9" t="n">
         <v>0</v>
       </c>
+      <c r="I11" s="8" t="inlineStr"/>
       <c r="J11" s="8" t="inlineStr"/>
       <c r="K11" s="8" t="inlineStr"/>
-      <c r="L11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1965,26 +1945,25 @@
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="7" t="n">
+      <c r="E12" s="7" t="n">
         <v>2</v>
       </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>A few proofs of concept</t>
+        </is>
+      </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>A few proofs of concept</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
           <t>Pilots run, but nothing reaches production</t>
         </is>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="H12" s="7" t="n">
         <v>25</v>
       </c>
+      <c r="I12" s="8" t="inlineStr"/>
       <c r="J12" s="8" t="inlineStr"/>
       <c r="K12" s="8" t="inlineStr"/>
-      <c r="L12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -2003,26 +1982,25 @@
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr"/>
-      <c r="E13" s="9" t="inlineStr"/>
-      <c r="F13" s="9" t="n">
+      <c r="E13" s="9" t="n">
         <v>3</v>
       </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Each business builds its own</t>
+        </is>
+      </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>Each business builds its own</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
           <t>Underwriting, claims and actuarial fund separately</t>
         </is>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="H13" s="9" t="n">
         <v>50</v>
       </c>
+      <c r="I13" s="8" t="inlineStr"/>
       <c r="J13" s="8" t="inlineStr"/>
       <c r="K13" s="8" t="inlineStr"/>
-      <c r="L13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -2041,26 +2019,25 @@
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr"/>
-      <c r="E14" s="7" t="inlineStr"/>
-      <c r="F14" s="7" t="n">
+      <c r="E14" s="7" t="n">
         <v>4</v>
       </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>One team funds the core</t>
+        </is>
+      </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>One team funds the core</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
           <t>A digital function funds and governs central pilots</t>
         </is>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="H14" s="7" t="n">
         <v>75</v>
       </c>
+      <c r="I14" s="8" t="inlineStr"/>
       <c r="J14" s="8" t="inlineStr"/>
       <c r="K14" s="8" t="inlineStr"/>
-      <c r="L14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -2079,26 +2056,25 @@
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr"/>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="9" t="n">
+      <c r="E15" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>An enterprise AI factory</t>
+        </is>
+      </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>An enterprise AI factory</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
           <t>One governed roadmap and shared funding across every line</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="H15" s="9" t="n">
         <v>100</v>
       </c>
+      <c r="I15" s="8" t="inlineStr"/>
       <c r="J15" s="8" t="inlineStr"/>
       <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -2121,30 +2097,25 @@
           <t>Could you explain an AI-driven decision to a regulator today?</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="n">
+      <c r="E16" s="7" t="n">
         <v>1</v>
       </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
           <t>Nothing is documented and nothing is testable</t>
         </is>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="H16" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I16" s="8" t="inlineStr"/>
       <c r="J16" s="8" t="inlineStr"/>
       <c r="K16" s="8" t="inlineStr"/>
-      <c r="L16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -2163,26 +2134,25 @@
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr"/>
-      <c r="E17" s="9" t="inlineStr"/>
-      <c r="F17" s="9" t="n">
+      <c r="E17" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Only after the fact</t>
+        </is>
+      </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Only after the fact</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
           <t>We could reconstruct it slowly, by hand</t>
         </is>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="H17" s="9" t="n">
         <v>25</v>
       </c>
+      <c r="I17" s="8" t="inlineStr"/>
       <c r="J17" s="8" t="inlineStr"/>
       <c r="K17" s="8" t="inlineStr"/>
-      <c r="L17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -2201,26 +2171,25 @@
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr"/>
-      <c r="E18" s="7" t="inlineStr"/>
-      <c r="F18" s="7" t="n">
+      <c r="E18" s="7" t="n">
         <v>3</v>
       </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Checked at the end</t>
+        </is>
+      </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Checked at the end</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
           <t>Bias and explainability are a final gate before release</t>
         </is>
       </c>
-      <c r="I18" s="7" t="n">
+      <c r="H18" s="7" t="n">
         <v>50</v>
       </c>
+      <c r="I18" s="8" t="inlineStr"/>
       <c r="J18" s="8" t="inlineStr"/>
       <c r="K18" s="8" t="inlineStr"/>
-      <c r="L18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -2239,26 +2208,25 @@
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr"/>
-      <c r="E19" s="9" t="inlineStr"/>
-      <c r="F19" s="9" t="n">
+      <c r="E19" s="9" t="n">
         <v>4</v>
       </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Built into the model</t>
+        </is>
+      </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>Built into the model</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
           <t>Explainability and bias testing sit in the architecture</t>
         </is>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="H19" s="9" t="n">
         <v>75</v>
       </c>
+      <c r="I19" s="8" t="inlineStr"/>
       <c r="J19" s="8" t="inlineStr"/>
       <c r="K19" s="8" t="inlineStr"/>
-      <c r="L19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -2277,26 +2245,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr"/>
-      <c r="E20" s="7" t="inlineStr"/>
-      <c r="F20" s="7" t="n">
+      <c r="E20" s="7" t="n">
         <v>5</v>
       </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Ready on demand</t>
+        </is>
+      </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Ready on demand</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
           <t>Audit trails and bias testing from the start, ready for NAIC and the EU AI Act</t>
         </is>
       </c>
-      <c r="I20" s="7" t="n">
+      <c r="H20" s="7" t="n">
         <v>100</v>
       </c>
+      <c r="I20" s="8" t="inlineStr"/>
       <c r="J20" s="8" t="inlineStr"/>
       <c r="K20" s="8" t="inlineStr"/>
-      <c r="L20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
@@ -2319,30 +2286,25 @@
           <t>What happens to the data from telematics, IoT and drones?</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="n">
+      <c r="E21" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>We do not collect it</t>
+        </is>
+      </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>We do not collect it</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
           <t>No sensor or telematics feed exists</t>
         </is>
       </c>
-      <c r="I21" s="9" t="n">
+      <c r="H21" s="9" t="n">
         <v>0</v>
       </c>
+      <c r="I21" s="8" t="inlineStr"/>
       <c r="J21" s="8" t="inlineStr"/>
       <c r="K21" s="8" t="inlineStr"/>
-      <c r="L21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -2361,26 +2323,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
-      <c r="E22" s="7" t="inlineStr"/>
-      <c r="F22" s="7" t="n">
+      <c r="E22" s="7" t="n">
         <v>2</v>
       </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Collected but unused</t>
+        </is>
+      </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Collected but unused</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
           <t>It lands somewhere and nothing reads it</t>
         </is>
       </c>
-      <c r="I22" s="7" t="n">
+      <c r="H22" s="7" t="n">
         <v>25</v>
       </c>
+      <c r="I22" s="8" t="inlineStr"/>
       <c r="J22" s="8" t="inlineStr"/>
       <c r="K22" s="8" t="inlineStr"/>
-      <c r="L22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
@@ -2399,26 +2360,25 @@
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr"/>
-      <c r="E23" s="9" t="inlineStr"/>
-      <c r="F23" s="9" t="n">
+      <c r="E23" s="9" t="n">
         <v>3</v>
       </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>A reporting by-product</t>
+        </is>
+      </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>A reporting by-product</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
           <t>It shows up in reports after the fact</t>
         </is>
       </c>
-      <c r="I23" s="9" t="n">
+      <c r="H23" s="9" t="n">
         <v>50</v>
       </c>
+      <c r="I23" s="8" t="inlineStr"/>
       <c r="J23" s="8" t="inlineStr"/>
       <c r="K23" s="8" t="inlineStr"/>
-      <c r="L23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -2437,26 +2397,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr"/>
-      <c r="E24" s="7" t="inlineStr"/>
-      <c r="F24" s="7" t="n">
+      <c r="E24" s="7" t="n">
         <v>4</v>
       </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Feeds one price</t>
+        </is>
+      </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Feeds one price</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
           <t>One feed is engineered into pricing as a real input</t>
         </is>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="H24" s="7" t="n">
         <v>75</v>
       </c>
+      <c r="I24" s="8" t="inlineStr"/>
       <c r="J24" s="8" t="inlineStr"/>
       <c r="K24" s="8" t="inlineStr"/>
-      <c r="L24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
@@ -2475,26 +2434,25 @@
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr"/>
-      <c r="E25" s="9" t="inlineStr"/>
-      <c r="F25" s="9" t="n">
+      <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>A first-class input</t>
+        </is>
+      </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>A first-class input</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
           <t>Pricing and claims use it live, with digital twins for exposure</t>
         </is>
       </c>
-      <c r="I25" s="9" t="n">
+      <c r="H25" s="9" t="n">
         <v>100</v>
       </c>
+      <c r="I25" s="8" t="inlineStr"/>
       <c r="J25" s="8" t="inlineStr"/>
       <c r="K25" s="8" t="inlineStr"/>
-      <c r="L25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -2517,30 +2475,25 @@
           <t>How are you handling the core platforms AI needs to reach?</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="n">
+      <c r="E26" s="7" t="n">
         <v>1</v>
       </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Frozen and untouchable</t>
+        </is>
+      </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Frozen and untouchable</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
           <t>Rating logic nobody fully understands, too risky to change</t>
         </is>
       </c>
-      <c r="I26" s="7" t="n">
+      <c r="H26" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I26" s="8" t="inlineStr"/>
       <c r="J26" s="8" t="inlineStr"/>
       <c r="K26" s="8" t="inlineStr"/>
-      <c r="L26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
@@ -2559,26 +2512,25 @@
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr"/>
-      <c r="E27" s="9" t="inlineStr"/>
-      <c r="F27" s="9" t="n">
+      <c r="E27" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Documented, not moving</t>
+        </is>
+      </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>Documented, not moving</t>
-        </is>
-      </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
           <t>The rules are written down but the platform is unchanged</t>
         </is>
       </c>
-      <c r="I27" s="9" t="n">
+      <c r="H27" s="9" t="n">
         <v>25</v>
       </c>
+      <c r="I27" s="8" t="inlineStr"/>
       <c r="J27" s="8" t="inlineStr"/>
       <c r="K27" s="8" t="inlineStr"/>
-      <c r="L27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -2597,26 +2549,25 @@
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr"/>
-      <c r="E28" s="7" t="inlineStr"/>
-      <c r="F28" s="7" t="n">
+      <c r="E28" s="7" t="n">
         <v>3</v>
       </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Rewriting by hand</t>
+        </is>
+      </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Rewriting by hand</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
           <t>Modernisation is under way module by module, manually</t>
         </is>
       </c>
-      <c r="I28" s="7" t="n">
+      <c r="H28" s="7" t="n">
         <v>50</v>
       </c>
+      <c r="I28" s="8" t="inlineStr"/>
       <c r="J28" s="8" t="inlineStr"/>
       <c r="K28" s="8" t="inlineStr"/>
-      <c r="L28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
@@ -2635,26 +2586,25 @@
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr"/>
-      <c r="E29" s="9" t="inlineStr"/>
-      <c r="F29" s="9" t="n">
+      <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>AI recovers the intent</t>
+        </is>
+      </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>AI recovers the intent</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
           <t>AI reads the legacy logic and rebuilds it as specification</t>
         </is>
       </c>
-      <c r="I29" s="9" t="n">
+      <c r="H29" s="9" t="n">
         <v>75</v>
       </c>
+      <c r="I29" s="8" t="inlineStr"/>
       <c r="J29" s="8" t="inlineStr"/>
       <c r="K29" s="8" t="inlineStr"/>
-      <c r="L29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -2673,26 +2623,25 @@
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr"/>
-      <c r="E30" s="7" t="inlineStr"/>
-      <c r="F30" s="7" t="n">
+      <c r="E30" s="7" t="n">
         <v>5</v>
       </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Modernising while live</t>
+        </is>
+      </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>Modernising while live</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
           <t>Module by module, with the book of business still trading</t>
         </is>
       </c>
-      <c r="I30" s="7" t="n">
+      <c r="H30" s="7" t="n">
         <v>100</v>
       </c>
+      <c r="I30" s="8" t="inlineStr"/>
       <c r="J30" s="8" t="inlineStr"/>
       <c r="K30" s="8" t="inlineStr"/>
-      <c r="L30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
@@ -2715,30 +2664,25 @@
           <t>How much of a full claims or underwriting journey does AI run?</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="n">
+      <c r="E31" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>None of it</t>
+        </is>
+      </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>None of it</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
           <t>Core workflows are manual from end to end</t>
         </is>
       </c>
-      <c r="I31" s="9" t="n">
+      <c r="H31" s="9" t="n">
         <v>0</v>
       </c>
+      <c r="I31" s="8" t="inlineStr"/>
       <c r="J31" s="8" t="inlineStr"/>
       <c r="K31" s="8" t="inlineStr"/>
-      <c r="L31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -2757,26 +2701,25 @@
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr"/>
-      <c r="E32" s="7" t="inlineStr"/>
-      <c r="F32" s="7" t="n">
+      <c r="E32" s="7" t="n">
         <v>2</v>
       </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Isolated tasks</t>
+        </is>
+      </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>Isolated tasks</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
           <t>Automation sits inside a workflow nobody redesigned</t>
         </is>
       </c>
-      <c r="I32" s="7" t="n">
+      <c r="H32" s="7" t="n">
         <v>25</v>
       </c>
+      <c r="I32" s="8" t="inlineStr"/>
       <c r="J32" s="8" t="inlineStr"/>
       <c r="K32" s="8" t="inlineStr"/>
-      <c r="L32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
@@ -2795,26 +2738,25 @@
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr"/>
-      <c r="E33" s="9" t="inlineStr"/>
-      <c r="F33" s="9" t="n">
+      <c r="E33" s="9" t="n">
         <v>3</v>
       </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>One journey rebuilt</t>
+        </is>
+      </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>One journey rebuilt</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
           <t>A single journey has been mapped and rebuilt around AI</t>
         </is>
       </c>
-      <c r="I33" s="9" t="n">
+      <c r="H33" s="9" t="n">
         <v>50</v>
       </c>
+      <c r="I33" s="8" t="inlineStr"/>
       <c r="J33" s="8" t="inlineStr"/>
       <c r="K33" s="8" t="inlineStr"/>
-      <c r="L33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -2833,26 +2775,25 @@
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr"/>
-      <c r="E34" s="7" t="inlineStr"/>
-      <c r="F34" s="7" t="n">
+      <c r="E34" s="7" t="n">
         <v>4</v>
       </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>Several journeys</t>
+        </is>
+      </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>Several journeys</t>
-        </is>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
           <t>Submission to bound, or FNOL to settlement, runs on agents</t>
         </is>
       </c>
-      <c r="I34" s="7" t="n">
+      <c r="H34" s="7" t="n">
         <v>75</v>
       </c>
+      <c r="I34" s="8" t="inlineStr"/>
       <c r="J34" s="8" t="inlineStr"/>
       <c r="K34" s="8" t="inlineStr"/>
-      <c r="L34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
@@ -2871,26 +2812,25 @@
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr"/>
-      <c r="E35" s="9" t="inlineStr"/>
-      <c r="F35" s="9" t="n">
+      <c r="E35" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Agents alongside people</t>
+        </is>
+      </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>Agents alongside people</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
           <t>Whole journeys redesigned, with agents working next to underwriters</t>
         </is>
       </c>
-      <c r="I35" s="9" t="n">
+      <c r="H35" s="9" t="n">
         <v>100</v>
       </c>
+      <c r="I35" s="8" t="inlineStr"/>
       <c r="J35" s="8" t="inlineStr"/>
       <c r="K35" s="8" t="inlineStr"/>
-      <c r="L35" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Unlock AI Value - content for client review.xlsx
+++ b/Unlock AI Value - content for client review.xlsx
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B30"/>
+  <dimension ref="B1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Insurance kiosk · exported 31 August 2026 from the build's content model</t>
+          <t>Insurance kiosk · exported 01 September 2026 from the build's content model</t>
         </is>
       </c>
     </row>
@@ -621,92 +621,99 @@
     <row r="17" ht="14" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2.  Benchmark medians are illustrative placeholders, not Infosys research. See 'Benchmark'.</t>
+          <t xml:space="preserve">        These six are now more urgent: case studies also appear during the diagnostic, so the pool of usable tiles is doing more work.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3.  The QR code on the final screen points nowhere yet. We need the destination URL.</t>
+          <t xml:space="preserve">    2.  Benchmark medians are illustrative placeholders, not Infosys research. See 'Benchmark'.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
       <c r="B19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    3.  The QR code on the final screen points nowhere yet. We need the destination URL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="14" customHeight="1">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    4.  The five-year forecast columns present today's case studies under future-dated headings. Flag if that framing is a problem.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="14" customHeight="1">
-      <c r="B20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="4" t="inlineStr">
+    <row r="21" ht="14" customHeight="1">
+      <c r="B21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Sheet guide</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="14" customHeight="1">
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Diagnostic questions    18 questions, 5 answers each (90 rows). Answer wording and the score behind each answer.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Value pools             The six pools: name, verb, description, three supporting facts.</t>
+          <t xml:space="preserve">    Diagnostic questions    18 questions, 5 answers each (90 rows). Answer wording and the score behind each answer.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="14" customHeight="1">
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Proof tiles             18 case-study tiles, 3 per pool. Six are unfilled.</t>
+          <t xml:space="preserve">    Value pools             The six pools: name, verb, description, three supporting facts.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="14" customHeight="1">
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Score band feedback     30 report blocks. What each score band tells a visitor, and the recommended move.</t>
+          <t xml:space="preserve">    Proof tiles             18 case-study tiles, 3 per pool. Six are unfilled. Two are shown mid-diagnostic.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="14" customHeight="1">
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Archetypes              Five overall positions a visitor can land in.</t>
+          <t xml:space="preserve">    Score band feedback     30 report blocks. What each score band tells a visitor, and the recommended move.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Role futures            How each role changes, matched from the badge.</t>
+          <t xml:space="preserve">    Archetypes              Five overall positions a visitor can land in.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Benchmark               Industry median per pool. Placeholder data.</t>
+          <t xml:space="preserve">    Role futures            How each role changes, matched from the badge.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Forecast lines          The three five-year outlook captions.</t>
+          <t xml:space="preserve">    Benchmark               Industry median per pool. Placeholder data.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
       <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Forecast lines          The three five-year outlook captions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="14" customHeight="1">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    Screen copy             Headlines, buttons and instructional text that is not pool-specific.</t>
         </is>
@@ -723,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -826,7 +833,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Three minutes. Six value pools. One blueprint.</t>
+          <t>Two minutes. Six value pools. One blueprint.</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr"/>
@@ -1146,7 +1153,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Question 1 of 18</t>
+          <t>Question 1 of 6</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr"/>
@@ -1156,17 +1163,17 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Identify</t>
+          <t>Proof (mid-diagnostic)</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Headline</t>
+          <t>Eyebrow</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tap your badge</t>
+          <t>[Value pool] · [Client]</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr"/>
@@ -1176,17 +1183,17 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Identify</t>
+          <t>Proof (mid-diagnostic)</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Lede</t>
+          <t>Progress</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Your badge carries your role, so the blueprint fits your job.</t>
+          <t>2 of 6 answered</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr"/>
@@ -1196,17 +1203,17 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Identify</t>
+          <t>Proof (mid-diagnostic)</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Reader state</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Waiting for badge</t>
+          <t>Continue</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr"/>
@@ -1221,12 +1228,12 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Headline</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Enter email manually</t>
+          <t>Tap your badge</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr"/>
@@ -1241,12 +1248,12 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Lede</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>See my results</t>
+          <t>Your badge carries your role, so the blueprint fits your job.</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr"/>
@@ -1261,12 +1268,12 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Reader state</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Waiting for badge</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr"/>
@@ -1276,17 +1283,17 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Results 1</t>
+          <t>Identify</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Eyebrow</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Your position</t>
+          <t>Enter email manually</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr"/>
@@ -1296,17 +1303,17 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Results 2</t>
+          <t>Identify</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Eyebrow</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Where you lead, where you lag</t>
+          <t>See my results</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr"/>
@@ -1316,17 +1323,17 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Results 2</t>
+          <t>Identify</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Headline</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Against the benchmark</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr"/>
@@ -1336,7 +1343,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Results 3</t>
+          <t>Results 1</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -1346,7 +1353,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>And your role</t>
+          <t>Your position</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr"/>
@@ -1356,17 +1363,17 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Results 3</t>
+          <t>Results 2</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Source note</t>
+          <t>Eyebrow</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Matched from your badge · playbook workforce transformation table</t>
+          <t>Where you lead, where you lag</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr"/>
@@ -1376,17 +1383,17 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Results 3</t>
+          <t>Results 2</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Eyebrow</t>
+          <t>Headline</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>The human constraint</t>
+          <t>Against the benchmark</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr"/>
@@ -1401,12 +1408,12 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>Eyebrow</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>The people most affected by AI are the domain experts who make it work. A team can have the model and still not trust it over decades of manual judgment, which is why the carriers that scale it own governance at board level and reward AI-enabled outcomes.</t>
+          <t>And your role</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr"/>
@@ -1416,17 +1423,17 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Results 4</t>
+          <t>Results 3</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Eyebrow</t>
+          <t>Source note</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Five-year view</t>
+          <t>Matched from your badge · playbook workforce transformation table</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr"/>
@@ -1436,17 +1443,17 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Results 4</t>
+          <t>Results 3</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Headline</t>
+          <t>Eyebrow</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Where the gap goes</t>
+          <t>The human constraint</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr"/>
@@ -1456,17 +1463,17 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Results 4</t>
+          <t>Results 3</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Lede</t>
+          <t>Body</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Unchanged, this is your five-year position.</t>
+          <t>The people most affected by AI are the domain experts who make it work. A team can have the model and still not trust it over decades of manual judgment, which is why the carriers that scale it own governance at board level and reward AI-enabled outcomes.</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr"/>
@@ -1476,7 +1483,7 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Results 4</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -1486,7 +1493,7 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Report dispatched</t>
+          <t>Five-year view</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr"/>
@@ -1496,7 +1503,7 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Results 4</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -1506,7 +1513,7 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>On its way</t>
+          <t>Where the gap goes</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr"/>
@@ -1516,17 +1523,17 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Results 4</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>Lede</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Sent to [email]. Three ways to get it back:</t>
+          <t>Unchanged, this is your five-year position.</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr"/>
@@ -1541,12 +1548,12 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Step 1</t>
+          <t>Eyebrow</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Scan the code above</t>
+          <t>Report dispatched</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr"/>
@@ -1561,12 +1568,12 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Step 2</t>
+          <t>Headline</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Open the email we just sent</t>
+          <t>On its way</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr"/>
@@ -1581,17 +1588,77 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Step 3</t>
+          <t>Body</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Scan your badge at the booth to see and discuss your result</t>
+          <t>Sent to [email]. Three ways to get it back:</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr"/>
       <c r="E44" s="8" t="inlineStr"/>
       <c r="F44" s="8" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Step 1</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Scan the code above</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr"/>
+      <c r="E45" s="8" t="inlineStr"/>
+      <c r="F45" s="8" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Step 2</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Open the email we just sent</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr"/>
+      <c r="E46" s="8" t="inlineStr"/>
+      <c r="F46" s="8" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Scan your badge at the booth to see and discuss your result</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr"/>
+      <c r="E47" s="8" t="inlineStr"/>
+      <c r="F47" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3168,7 +3235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3193,132 +3260,101 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>Two of these tiles now also appear during the diagnostic, on their own screen after the second and fourth questions, per Anshul's note that proof should land while someone is still answering. The kiosk picks the lowest scoring pool answered so far and skips any amber row, so an unfilled tile is never shown on the floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
           <t>Named carriers appear on a public show floor. Confirm each one is cleared for use.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Value pool</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Tile title</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Headline metric</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Approved? (Y/N)</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Revised copy</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Client comments</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>_p</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Data for AI</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Everest Re</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Treaty digitization</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>100% of treaties digitized</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Decades of treaty wordings trapped in scanned files. Document AI and Neural Connect turned them into a searchable layer with natural-language querying over NATCAT exposure.</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Data for AI</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Ameritas</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Provider fee optimisation</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>$1.2M recurring annual saving</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>Dental and vision insurer. ML anomaly detection over fee schedules, with market segmentation replacing a one-size-fits-all contracting model.</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr"/>
       <c r="H6" s="8" t="inlineStr"/>
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="b">
@@ -3326,37 +3362,37 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Data for AI</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>One America</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Competitive intelligence</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Manual research effort removed</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Leadership had no real-time view of competitor and regulatory movement. An agent aggregates sources into a single briefing on request.</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr"/>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Ameritas</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Provider fee optimisation</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>$1.2M recurring annual saving</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Dental and vision insurer. ML anomaly detection over fee schedules, with market segmentation replacing a one-size-fits-all contracting model.</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr"/>
       <c r="H7" s="8" t="inlineStr"/>
       <c r="I7" s="8" t="inlineStr"/>
       <c r="J7" s="8" t="b">
@@ -3364,37 +3400,37 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Data for AI</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>US carrier</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>AI strategy and COE</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>150+ opportunities prioritised</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>Workers’ compensation, E&amp;S and reinsurance specialist. Fragmented initiatives with no unified governance; Infosys defined the target architecture and a use case scoring methodology.</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>One America</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Competitive intelligence</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Manual research effort removed</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Leadership had no real-time view of competitor and regulatory movement. An agent aggregates sources into a single briefing on request.</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr"/>
       <c r="H8" s="8" t="inlineStr"/>
       <c r="I8" s="8" t="inlineStr"/>
       <c r="J8" s="8" t="b">
@@ -3402,37 +3438,37 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>AI Strategy &amp; Engineering</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Ameritas</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>AI Factory model</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>45K+ hours realised</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Multi-line mutual insurer. An AI Factory operating model with dedicated PODs and governance; 80+ opportunities identified and prioritised across business functions.</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr"/>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>US carrier</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>AI strategy and COE</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>150+ opportunities prioritised</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Workers’ compensation, E&amp;S and reinsurance specialist. Fragmented initiatives with no unified governance; Infosys defined the target architecture and a use case scoring methodology.</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr"/>
       <c r="H9" s="8" t="inlineStr"/>
       <c r="I9" s="8" t="inlineStr"/>
       <c r="J9" s="8" t="b">
@@ -3440,37 +3476,37 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>AI Strategy &amp; Engineering</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Northwestern Mutual</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>AI COE foundation</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>Standardised intake and guardrails</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>Large US mutual life insurer. Five-stream COE covering structured intake, value realisation, Responsible AI, backlog grooming and AI architecture.</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr"/>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Ameritas</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>AI Factory model</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>45K+ hours realised</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Multi-line mutual insurer. An AI Factory operating model with dedicated PODs and governance; 80+ opportunities identified and prioritised across business functions.</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr"/>
       <c r="H10" s="8" t="inlineStr"/>
       <c r="I10" s="8" t="inlineStr"/>
       <c r="J10" s="8" t="b">
@@ -3478,37 +3514,37 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>AI Trust</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>AI Strategy &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Ameritas</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>AI-first risk and compliance</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>30% productivity improvement</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>Substituted from the use case register: continuous risk scoring, automated evidence compilation and control testing, with human experts on interpretation and high-risk exceptions.</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr"/>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Northwestern Mutual</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>AI COE foundation</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Standardised intake and guardrails</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Large US mutual life insurer. Five-stream COE covering structured intake, value realisation, Responsible AI, backlog grooming and AI architecture.</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr"/>
       <c r="H11" s="8" t="inlineStr"/>
       <c r="I11" s="8" t="inlineStr"/>
       <c r="J11" s="8" t="b">
@@ -3516,37 +3552,41 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>AI Trust</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>NEEDS CONTENT</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr"/>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>NAIC governance proof</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>Infosys to supply</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>The playbook’s AI Trust section carries an unfilled case study placeholder. A named governance engagement is needed.</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr"/>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Ameritas</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>AI-first risk and compliance</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>30% productivity improvement</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Substituted from the use case register: continuous risk scoring, automated evidence compilation and control testing, with human experts on interpretation and high-risk exceptions.</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr"/>
       <c r="H12" s="8" t="inlineStr"/>
       <c r="I12" s="8" t="inlineStr"/>
       <c r="J12" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3563,7 +3603,7 @@
       <c r="C13" s="10" t="inlineStr"/>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Explainability in underwriting</t>
+          <t>NAIC governance proof</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
@@ -3573,7 +3613,7 @@
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>Glass-box auditability is central to the pillar’s argument but no client proof point is documented.</t>
+          <t>The playbook’s AI Trust section carries an unfilled case study placeholder. A named governance engagement is needed.</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr"/>
@@ -3586,7 +3626,7 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Physical AI</t>
+          <t>AI Trust</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -3597,7 +3637,7 @@
       <c r="C14" s="10" t="inlineStr"/>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Telematics into pricing</t>
+          <t>Explainability in underwriting</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -3607,7 +3647,7 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>The playbook’s Physical AI section carries an unfilled case study placeholder and the use case register has no Physical AI row. Infosys to supply.</t>
+          <t>Glass-box auditability is central to the pillar’s argument but no client proof point is documented.</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr"/>
@@ -3631,7 +3671,7 @@
       <c r="C15" s="10" t="inlineStr"/>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Drone claims inspection</t>
+          <t>Telematics into pricing</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -3641,7 +3681,7 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Described in the playbook as a capability, catastrophe damage validated in hours rather than weeks, but with no client engagement documented.</t>
+          <t>The playbook’s Physical AI section carries an unfilled case study placeholder and the use case register has no Physical AI row. Infosys to supply.</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr"/>
@@ -3665,7 +3705,7 @@
       <c r="C16" s="10" t="inlineStr"/>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Digital twin exposure modelling</t>
+          <t>Drone claims inspection</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -3675,7 +3715,7 @@
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>Digital twins of insured properties and fleets appear in the playbook narrative with no supporting engagement.</t>
+          <t>Described in the playbook as a capability, catastrophe damage validated in hours rather than weeks, but with no client engagement documented.</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr"/>
@@ -3686,75 +3726,71 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Agentic Legacy Modernization</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>MassMutual</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Policy migration extraction</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>F1 99.2% across 9,100 pages</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>Product rules scattered across 1,132 documents. IPMS industrialised extraction, cutting BRS time-to-create by over 50% and delivering 15 functionalities in 12 weeks.</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr"/>
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Physical AI</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>NEEDS CONTENT</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr"/>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Digital twin exposure modelling</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Infosys to supply</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>Digital twins of insured properties and fleets appear in the playbook narrative with no supporting engagement.</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr"/>
       <c r="H17" s="8" t="inlineStr"/>
       <c r="I17" s="8" t="inlineStr"/>
       <c r="J17" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Agentic Legacy Modernization</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Northwestern Mutual</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Informatica ETL reverse engineering</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>~70% less documentation effort</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>1,000+ legacy ETL mappings moving to Databricks. Graph RAG over exported XML recovered transformation rules into SME validation workbooks.</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>MassMutual</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Policy migration extraction</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>F1 99.2% across 9,100 pages</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Product rules scattered across 1,132 documents. IPMS industrialised extraction, cutting BRS time-to-create by over 50% and delivering 15 functionalities in 12 weeks.</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr"/>
       <c r="H18" s="8" t="inlineStr"/>
       <c r="I18" s="8" t="inlineStr"/>
       <c r="J18" s="8" t="b">
@@ -3762,109 +3798,109 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Agentic Legacy Modernization</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>NEEDS CONTENT</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr"/>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Third proof point</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>Infosys to supply</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>The playbook and use case register contain two Agentic Legacy engagements. A third is needed to balance this pool against the others.</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr"/>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Northwestern Mutual</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Informatica ETL reverse engineering</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>~70% less documentation effort</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>1,000+ legacy ETL mappings moving to Databricks. Graph RAG over exported XML recovered transformation rules into SME validation workbooks.</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr"/>
       <c r="H19" s="8" t="inlineStr"/>
       <c r="I19" s="8" t="inlineStr"/>
       <c r="J19" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>Process AI</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Allied World</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Underwriting workbench</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>Request-to-bind up 50%</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>Underwriters spent 1–2 hours per submission just qualifying it. AI Next orchestrated triage, auto-decline and IGO/NIGO classification; manual effort and operations TCO both halved.</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr"/>
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Agentic Legacy Modernization</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>NEEDS CONTENT</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr"/>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Third proof point</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Infosys to supply</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>The playbook and use case register contain two Agentic Legacy engagements. A third is needed to balance this pool against the others.</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr"/>
       <c r="H20" s="8" t="inlineStr"/>
       <c r="I20" s="8" t="inlineStr"/>
       <c r="J20" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Process AI</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>One America</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Hardship withdrawals</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>10–14 days to under 30 minutes</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Retirement benefits processing cost over $100 per transaction with NIGO above 65%. Straight-through processing cut cost under $10 and NIGO below 5%.</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr"/>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Allied World</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Underwriting workbench</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Request-to-bind up 50%</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Underwriters spent 1–2 hours per submission just qualifying it. AI Next orchestrated triage, auto-decline and IGO/NIGO classification; manual effort and operations TCO both halved.</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr"/>
       <c r="H21" s="8" t="inlineStr"/>
       <c r="I21" s="8" t="inlineStr"/>
       <c r="J21" s="8" t="b">
@@ -3872,40 +3908,78 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Process AI</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>SageSure</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Statement of Values processing</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>80% less manual effort</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>Submissions arrived as emails, PDFs, ACORD forms and loss runs. An AI Foundry pipeline extracts, validates and standardises into a rating-ready output, with humans on exceptions only.</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr"/>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>One America</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Hardship withdrawals</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>10–14 days to under 30 minutes</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Retirement benefits processing cost over $100 per transaction with NIGO above 65%. Straight-through processing cut cost under $10 and NIGO below 5%.</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr"/>
       <c r="H22" s="8" t="inlineStr"/>
       <c r="I22" s="8" t="inlineStr"/>
       <c r="J22" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Process AI</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>SageSure</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Statement of Values processing</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>80% less manual effort</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Submissions arrived as emails, PDFs, ACORD forms and loss runs. An AI Foundry pipeline extracts, validates and standardises into a rating-ready output, with humans on exceptions only.</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr"/>
+      <c r="I23" s="8" t="inlineStr"/>
+      <c r="J23" s="8" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Unlock AI Value - content for client review.xlsx
+++ b/Unlock AI Value - content for client review.xlsx
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Insurance kiosk · exported 01 September 2026 from the build's content model</t>
+          <t>Insurance kiosk · exported 02 September 2026 from the build's content model</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
     <row r="17" ht="14" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">        These six are now more urgent: case studies also appear during the diagnostic, so the pool of usable tiles is doing more work.</t>
+          <t xml:space="preserve">        These six are now more urgent: one case study per pool also appears on that pool's diagnostic question, so Physical AI's question has no proof on it at all.</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
     <row r="25" ht="14" customHeight="1">
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Proof tiles             18 case-study tiles, 3 per pool. Six are unfilled. Two are shown mid-diagnostic.</t>
+          <t xml:space="preserve">    Proof tiles             18 case-study tiles, 3 per pool. Six are unfilled. One per pool also shows during the diagnostic.</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1163,12 +1163,12 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Proof (mid-diagnostic)</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Eyebrow</t>
+          <t>Case card eyebrow</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Proof (mid-diagnostic)</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Case card link</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>2 of 6 answered</t>
+          <t>Read the case</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr"/>
@@ -1203,17 +1203,17 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Proof (mid-diagnostic)</t>
+          <t>Identify</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Headline</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Continue</t>
+          <t>Tap your badge</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr"/>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Headline</t>
+          <t>Lede</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Tap your badge</t>
+          <t>Your badge carries your role, so the blueprint fits your job.</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Lede</t>
+          <t>Reader state</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Your badge carries your role, so the blueprint fits your job.</t>
+          <t>Waiting for badge</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr"/>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Reader state</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Waiting for badge</t>
+          <t>Enter email manually</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr"/>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Enter email manually</t>
+          <t>See my results</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr"/>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>See my results</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr"/>
@@ -1323,17 +1323,17 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Identify</t>
+          <t>Results 1</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Eyebrow</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Your position</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr"/>
@@ -1343,7 +1343,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Results 1</t>
+          <t>Results 2</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Your position</t>
+          <t>Where you lead, where you lag</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr"/>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Eyebrow</t>
+          <t>Headline</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Where you lead, where you lag</t>
+          <t>Against the benchmark</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr"/>
@@ -1383,17 +1383,17 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Results 2</t>
+          <t>Results 3</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Headline</t>
+          <t>Eyebrow</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Against the benchmark</t>
+          <t>And your role</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr"/>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Eyebrow</t>
+          <t>Source note</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>And your role</t>
+          <t>Matched from your badge · playbook workforce transformation table</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr"/>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Source note</t>
+          <t>Eyebrow</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Matched from your badge · playbook workforce transformation table</t>
+          <t>The human constraint</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr"/>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Eyebrow</t>
+          <t>Body</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>The human constraint</t>
+          <t>The people most affected by AI are the domain experts who make it work. A team can have the model and still not trust it over decades of manual judgment, which is why the carriers that scale it own governance at board level and reward AI-enabled outcomes.</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr"/>
@@ -1463,17 +1463,17 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Results 3</t>
+          <t>Results 4</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>Eyebrow</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>The people most affected by AI are the domain experts who make it work. A team can have the model and still not trust it over decades of manual judgment, which is why the carriers that scale it own governance at board level and reward AI-enabled outcomes.</t>
+          <t>Five-year view</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr"/>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Eyebrow</t>
+          <t>Headline</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Five-year view</t>
+          <t>Where the gap goes</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr"/>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Headline</t>
+          <t>Lede</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Where the gap goes</t>
+          <t>Unchanged, this is your five-year position.</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr"/>
@@ -1523,17 +1523,17 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Results 4</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Lede</t>
+          <t>Eyebrow</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Unchanged, this is your five-year position.</t>
+          <t>Report dispatched</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr"/>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Eyebrow</t>
+          <t>Headline</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Report dispatched</t>
+          <t>On its way</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr"/>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Headline</t>
+          <t>Body</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>On its way</t>
+          <t>Sent to [email]. Three ways to get it back:</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr"/>
@@ -1588,12 +1588,12 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>Step 1</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Sent to [email]. Three ways to get it back:</t>
+          <t>Scan the code above</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr"/>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Step 1</t>
+          <t>Step 2</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Scan the code above</t>
+          <t>Open the email we just sent</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr"/>
@@ -1628,37 +1628,17 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Step 2</t>
+          <t>Step 3</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Open the email we just sent</t>
+          <t>Scan your badge at the booth to see and discuss your result</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr"/>
       <c r="E46" s="8" t="inlineStr"/>
       <c r="F46" s="8" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="9" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>Step 3</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>Scan your badge at the booth to see and discuss your result</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr"/>
-      <c r="E47" s="8" t="inlineStr"/>
-      <c r="F47" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3260,7 +3240,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Two of these tiles now also appear during the diagnostic, on their own screen after the second and fourth questions, per Anshul's note that proof should land while someone is still answering. The kiosk picks the lowest scoring pool answered so far and skips any amber row, so an unfilled tile is never shown on the floor.</t>
+          <t>One of these appears on each diagnostic question screen, next to the question for its own value pool, per Anshul's note that proof should land while someone is still answering. The first cleared tile in each pool is used, and amber rows are skipped, so Physical AI currently shows no case study at all on its question.</t>
         </is>
       </c>
     </row>

--- a/Unlock AI Value - content for client review.xlsx
+++ b/Unlock AI Value - content for client review.xlsx
@@ -3240,7 +3240,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>One of these appears on each diagnostic question screen, next to the question for its own value pool, per Anshul's note that proof should land while someone is still answering. The first cleared tile in each pool is used, and amber rows are skipped, so Physical AI currently shows no case study at all on its question.</t>
+          <t>One of these appears in each diagnostic question panel, between the answer and Next, for that question's own value pool, per Anshul's note that proof should land while someone is still answering. The first cleared tile in each pool is used, and amber rows are skipped, so Physical AI currently shows no case study at all on its question.</t>
         </is>
       </c>
     </row>

--- a/Unlock AI Value - content for client review.xlsx
+++ b/Unlock AI Value - content for client review.xlsx
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B31"/>
+  <dimension ref="B1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -642,78 +642,85 @@
     <row r="20" ht="14" customHeight="1">
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    5.  Case study clients are masked to descriptors, so no carrier is named anywhere in the build. If any are cleared for use by name, tell us which and we will restore them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="14" customHeight="1">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    4.  The five-year forecast columns present today's case studies under future-dated headings. Flag if that framing is a problem.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="14" customHeight="1">
-      <c r="B21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="4" t="inlineStr">
+    <row r="22" ht="14" customHeight="1">
+      <c r="B22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Sheet guide</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="14" customHeight="1">
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Diagnostic questions    18 questions, 5 answers each (90 rows). Answer wording and the score behind each answer.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="14" customHeight="1">
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Value pools             The six pools: name, verb, description, three supporting facts.</t>
+          <t xml:space="preserve">    Diagnostic questions    18 questions, 5 answers each (90 rows). Answer wording and the score behind each answer.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="14" customHeight="1">
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Proof tiles             18 case-study tiles, 3 per pool. Six are unfilled. One per pool also shows during the diagnostic.</t>
+          <t xml:space="preserve">    Value pools             The six pools: name, verb, description, three supporting facts.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="14" customHeight="1">
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Score band feedback     30 report blocks. What each score band tells a visitor, and the recommended move.</t>
+          <t xml:space="preserve">    Proof tiles             18 case-study tiles, 3 per pool. Six are unfilled, and client names are masked. One per pool also shows during the diagnostic.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Archetypes              Five overall positions a visitor can land in.</t>
+          <t xml:space="preserve">    Score band feedback     30 report blocks. What each score band tells a visitor, and the recommended move.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Role futures            How each role changes, matched from the badge.</t>
+          <t xml:space="preserve">    Archetypes              Five overall positions a visitor can land in.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Benchmark               Industry median per pool. Placeholder data.</t>
+          <t xml:space="preserve">    Role futures            How each role changes, matched from the badge.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Forecast lines          The three five-year outlook captions.</t>
+          <t xml:space="preserve">    Benchmark               Industry median per pool. Placeholder data.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1">
       <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Forecast lines          The three five-year outlook captions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    Screen copy             Headlines, buttons and instructional text that is not pool-specific.</t>
         </is>
@@ -3157,7 +3164,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>99.2% extraction accuracy (F1) at MassMutual</t>
+          <t>99.2% extraction accuracy (F1) on legacy product rules</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr"/>
@@ -3197,7 +3204,7 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>Manual underwriting effort cut 50% at Allied World</t>
+          <t>Manual underwriting effort cut 50% at a global specialty insurer</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr"/>
@@ -3247,7 +3254,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Named carriers appear on a public show floor. Confirm each one is cleared for use.</t>
+          <t>Client names are masked, per your note that all case study names go without client references. The Client column carries a descriptor instead. Tell us which carriers are cleared by name and we will put them back.</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3271,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Client (masked)</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -3316,7 +3323,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Everest Re</t>
+          <t>Global reinsurer</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -3354,7 +3361,7 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Ameritas</t>
+          <t>US dental and vision insurer</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -3369,7 +3376,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Dental and vision insurer. ML anomaly detection over fee schedules, with market segmentation replacing a one-size-fits-all contracting model.</t>
+          <t>ML anomaly detection over fee schedules, with market segmentation replacing a one-size-fits-all contracting model.</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr"/>
@@ -3392,7 +3399,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>One America</t>
+          <t>US retirement and life insurer</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -3468,7 +3475,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Ameritas</t>
+          <t>US multi-line mutual insurer</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -3483,7 +3490,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Multi-line mutual insurer. An AI Factory operating model with dedicated PODs and governance; 80+ opportunities identified and prioritised across business functions.</t>
+          <t>An AI Factory operating model with dedicated PODs and governance; 80+ opportunities identified and prioritised across business functions.</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr"/>
@@ -3506,7 +3513,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>Large US mutual life insurer</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -3521,7 +3528,7 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Large US mutual life insurer. Five-stream COE covering structured intake, value realisation, Responsible AI, backlog grooming and AI architecture.</t>
+          <t>Five-stream COE covering structured intake, value realisation, Responsible AI, backlog grooming and AI architecture.</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr"/>
@@ -3544,7 +3551,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Ameritas</t>
+          <t>US insurance group</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -3752,7 +3759,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>MassMutual</t>
+          <t>US life and annuities carrier</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -3790,7 +3797,7 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>US mutual insurer</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -3862,7 +3869,7 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Allied World</t>
+          <t>Global specialty insurer</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -3900,7 +3907,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>One America</t>
+          <t>US retirement benefits provider</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -3938,7 +3945,7 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>SageSure</t>
+          <t>US property insurer</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">

--- a/Unlock AI Value - content for client review.xlsx
+++ b/Unlock AI Value - content for client review.xlsx
@@ -628,7 +628,7 @@
     <row r="18" ht="14" customHeight="1">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2.  Benchmark medians are illustrative placeholders, not Infosys research. See 'Benchmark'.</t>
+          <t xml:space="preserve">    2.  Benchmark. Agreed the industry baseline comes from Gartner. Three things are needed and all three need Gartner access: the six baseline figures on a 0-100 scale, the exact reference (report title, author, publication date), and confirmation that Gartner's reprint terms allow attribution on a public kiosk. Until then the figures on screen stay labelled as placeholders and the fine print says so. See 'Benchmark'.</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
     <row r="30" ht="14" customHeight="1">
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Benchmark               Industry median per pool. Placeholder data.</t>
+          <t xml:space="preserve">    Benchmark               Industry baseline per pool, to come from Gartner. Placeholder figures today.</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5428,119 +5428,83 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Kiosk currently labels this: "Illustrative industry benchmark · pending Infosys data"</t>
+          <t>Kiosk currently labels this: "Illustrative industry benchmark · Gartner figures pending"</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Every figure here is a placeholder we invented for layout. Replace with Infosys research, or we keep the 'illustrative' label on the screen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+          <t>Fine print on the results screen and the final screen currently reads: "Benchmark to be sourced from Gartner research. The comparison figures shown are illustrative placeholders, not Gartner data."</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Every figure in this sheet is a placeholder we invented for layout. None of them is Gartner data and the screen does not claim otherwise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>To go live we need three things from a Gartner seat: these six figures on the 0-100 scale, the exact reference to cite (report title, author, publication date), and confirmation that Gartner's reprint terms permit attribution on a public kiosk at a show. The third one is the long pole, so worth starting early.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Once they arrive the fine print becomes: "Industry baseline from Gartner research on AI adoption in insurance. Your score for each value pool is compared against that baseline." plus the citation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Value pool</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Industry median (placeholder)</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Gartner baseline (placeholder today)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Max score</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Approved? (Y/N)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Revised copy</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Client comments</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>_p</t>
         </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Data for AI</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="C5" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="D5" s="10" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>AI Trust</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="D7" s="10" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="8" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Physical AI</t>
+          <t>Data for AI</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>100</v>
@@ -5555,11 +5519,11 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Agentic Legacy Modernization</t>
+          <t>AI Strategy &amp; Engineering</t>
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C9" s="10" t="n">
         <v>100</v>
@@ -5574,11 +5538,11 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Process AI</t>
+          <t>AI Trust</t>
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C10" s="10" t="n">
         <v>100</v>
@@ -5587,6 +5551,63 @@
       <c r="E10" s="8" t="inlineStr"/>
       <c r="F10" s="8" t="inlineStr"/>
       <c r="G10" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Physical AI</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" s="10" t="inlineStr"/>
+      <c r="E11" s="8" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr"/>
+      <c r="G11" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Agentic Legacy Modernization</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" s="10" t="inlineStr"/>
+      <c r="E12" s="8" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
+      <c r="G12" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Process AI</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" s="10" t="inlineStr"/>
+      <c r="E13" s="8" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr"/>
+      <c r="G13" s="8" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Unlock AI Value - content for client review.xlsx
+++ b/Unlock AI Value - content for client review.xlsx
@@ -5413,7 +5413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5428,79 +5428,91 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Kiosk currently labels this: "Illustrative industry benchmark · Gartner figures pending"</t>
+          <t>Fine print on the results screen and the final screen currently reads: "Benchmark to be sourced from Gartner research. The comparison figures shown are illustrative placeholders, not Gartner data."</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fine print on the results screen and the final screen currently reads: "Benchmark to be sourced from Gartner research. The comparison figures shown are illustrative placeholders, not Gartner data."</t>
+          <t>Every figure in this sheet is a placeholder we invented for layout. None of them is Gartner data and the screen does not claim otherwise.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Every figure in this sheet is a placeholder we invented for layout. None of them is Gartner data and the screen does not claim otherwise.</t>
+          <t>To go live we need three things from a Gartner seat: these six figures on the 0-100 scale, the exact reference to cite (report title, author, publication date), and confirmation that Gartner's reprint terms permit attribution on a public kiosk at a show. The third one is the long pole, so worth starting early.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>To go live we need three things from a Gartner seat: these six figures on the 0-100 scale, the exact reference to cite (report title, author, publication date), and confirmation that Gartner's reprint terms permit attribution on a public kiosk at a show. The third one is the long pole, so worth starting early.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
           <t>Once they arrive the fine print becomes: "Industry baseline from Gartner research on AI adoption in insurance. Your score for each value pool is compared against that baseline." plus the citation.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Value pool</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Gartner baseline (placeholder today)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Max score</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Approved? (Y/N)</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Revised copy</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Client comments</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>_p</t>
         </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Data for AI</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" s="10" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr"/>
+      <c r="G7" s="8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Data for AI</t>
+          <t>AI Strategy &amp; Engineering</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
@@ -5519,7 +5531,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>AI Strategy &amp; Engineering</t>
+          <t>AI Trust</t>
         </is>
       </c>
       <c r="B9" s="10" t="n">
@@ -5538,11 +5550,11 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>AI Trust</t>
+          <t>Physical AI</t>
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C10" s="10" t="n">
         <v>100</v>
@@ -5557,11 +5569,11 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Physical AI</t>
+          <t>Agentic Legacy Modernization</t>
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>100</v>
@@ -5576,11 +5588,11 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Agentic Legacy Modernization</t>
+          <t>Process AI</t>
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C12" s="10" t="n">
         <v>100</v>
@@ -5589,25 +5601,6 @@
       <c r="E12" s="8" t="inlineStr"/>
       <c r="F12" s="8" t="inlineStr"/>
       <c r="G12" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Process AI</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="C13" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" s="10" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
-      <c r="G13" s="8" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Unlock AI Value - content for client review.xlsx
+++ b/Unlock AI Value - content for client review.xlsx
@@ -13,10 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proof tiles" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Score band feedback" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archetypes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Role futures" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast lines" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screen copy" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast lines" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screen copy" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -511,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B32"/>
+  <dimension ref="B1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -701,951 +700,23 @@
     <row r="29" ht="14" customHeight="1">
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Role futures            How each role changes, matched from the badge.</t>
+          <t xml:space="preserve">    Benchmark               Industry baseline per pool, to come from Gartner. Placeholder figures today.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Benchmark               Industry baseline per pool, to come from Gartner. Placeholder figures today.</t>
+          <t xml:space="preserve">    Forecast lines          The three five-year outlook captions.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1">
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Forecast lines          The three five-year outlook captions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="14" customHeight="1">
-      <c r="B32" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">    Screen copy             Headlines, buttons and instructional text that is not pool-specific.</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="86" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Fixed copy that is not pool- or score-specific. Square brackets are filled in live by the kiosk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Screen</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Element</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Approved? (Y/N)</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>Revised copy</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>Client comments</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Attract</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Eyebrow</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>AI-First Value Framework</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Attract</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Headline</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Are you ready to unlock your AI Value in insurance?</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Attract</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Subhead</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Two minutes. Six value pools. One blueprint.</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Attract</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Touch cue</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Touch to begin</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>All screens</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Brand line</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Unlock AI Value in Insurance</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Framework screen</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Eyebrow</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>An Infosys framework</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Framework screen</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Headline</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Six pools of AI value in insurance</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Framework screen</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Lede</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Infosys' own model for insurance, not an industry standard. Each pool is somewhere AI creates measurable value for carriers, and somewhere programmes commonly stall.</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Framework screen</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Gist: AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>One operating model, instead of pilots scattered across the business</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Framework screen</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Gist: Data for AI</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Policy, claims and treaty data made AI-ready and audit-ready</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Framework screen</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Gist: Process AI</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Whole journeys redesigned, not task-level automation inside old ones</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr"/>
-      <c r="F14" s="8" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Framework screen</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Gist: Agentic Legacy Modernization</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Core platforms modernised module by module, while the book stays live</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Framework screen</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Gist: Physical AI</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Telematics, IoT and drone data as a pricing and claims input</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr"/>
-      <c r="E16" s="8" t="inlineStr"/>
-      <c r="F16" s="8" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Framework screen</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Gist: AI Trust</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Explainability, bias testing and audit trails built in from the start</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr"/>
-      <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="8" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Framework screen</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Button (primary)</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Explore the six pools</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr"/>
-      <c r="E18" s="8" t="inlineStr"/>
-      <c r="F18" s="8" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Framework screen</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Button (secondary)</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Start the diagnostic</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr"/>
-      <c r="E19" s="8" t="inlineStr"/>
-      <c r="F19" s="8" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Explore</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Instruction</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Tap a value pool to explore</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr"/>
-      <c r="E20" s="8" t="inlineStr"/>
-      <c r="F20" s="8" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Explore</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Button</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Start the diagnostic</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr"/>
-      <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="8" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Diagnostic</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Progress</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Question 1 of 6</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr"/>
-      <c r="E22" s="8" t="inlineStr"/>
-      <c r="F22" s="8" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>Diagnostic</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Case card eyebrow</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>[Value pool] · [Client]</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr"/>
-      <c r="E23" s="8" t="inlineStr"/>
-      <c r="F23" s="8" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Diagnostic</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Case card link</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Read the case</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr"/>
-      <c r="E24" s="8" t="inlineStr"/>
-      <c r="F24" s="8" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>Identify</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Headline</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Tap your badge</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr"/>
-      <c r="E25" s="8" t="inlineStr"/>
-      <c r="F25" s="8" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Identify</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Lede</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Your badge carries your role, so the blueprint fits your job.</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr"/>
-      <c r="E26" s="8" t="inlineStr"/>
-      <c r="F26" s="8" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>Identify</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Reader state</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Waiting for badge</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr"/>
-      <c r="E27" s="8" t="inlineStr"/>
-      <c r="F27" s="8" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Identify</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Button</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Enter email manually</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr"/>
-      <c r="E28" s="8" t="inlineStr"/>
-      <c r="F28" s="8" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Identify</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Button</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>See my results</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr"/>
-      <c r="E29" s="8" t="inlineStr"/>
-      <c r="F29" s="8" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Identify</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Button</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Cancel</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr"/>
-      <c r="E30" s="8" t="inlineStr"/>
-      <c r="F30" s="8" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>Results 1</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>Eyebrow</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Your position</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr"/>
-      <c r="E31" s="8" t="inlineStr"/>
-      <c r="F31" s="8" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Results 2</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Eyebrow</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Where you lead, where you lag</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr"/>
-      <c r="E32" s="8" t="inlineStr"/>
-      <c r="F32" s="8" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>Results 2</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>Headline</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Against the benchmark</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr"/>
-      <c r="E33" s="8" t="inlineStr"/>
-      <c r="F33" s="8" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Results 3</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Eyebrow</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>And your role</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr"/>
-      <c r="E34" s="8" t="inlineStr"/>
-      <c r="F34" s="8" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>Results 3</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>Source note</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Matched from your badge · playbook workforce transformation table</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr"/>
-      <c r="E35" s="8" t="inlineStr"/>
-      <c r="F35" s="8" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Results 3</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Eyebrow</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>The human constraint</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr"/>
-      <c r="E36" s="8" t="inlineStr"/>
-      <c r="F36" s="8" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>Results 3</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>Body</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>The people most affected by AI are the domain experts who make it work. A team can have the model and still not trust it over decades of manual judgment, which is why the carriers that scale it own governance at board level and reward AI-enabled outcomes.</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr"/>
-      <c r="E37" s="8" t="inlineStr"/>
-      <c r="F37" s="8" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>Results 4</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Eyebrow</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Five-year view</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr"/>
-      <c r="E38" s="8" t="inlineStr"/>
-      <c r="F38" s="8" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>Results 4</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>Headline</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>Where the gap goes</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr"/>
-      <c r="E39" s="8" t="inlineStr"/>
-      <c r="F39" s="8" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>Results 4</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Lede</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>Unchanged, this is your five-year position.</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr"/>
-      <c r="E40" s="8" t="inlineStr"/>
-      <c r="F40" s="8" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>Eyebrow</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>Report dispatched</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr"/>
-      <c r="E41" s="8" t="inlineStr"/>
-      <c r="F41" s="8" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Headline</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>On its way</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr"/>
-      <c r="E42" s="8" t="inlineStr"/>
-      <c r="F42" s="8" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>Body</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Sent to [email]. Three ways to get it back:</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr"/>
-      <c r="E43" s="8" t="inlineStr"/>
-      <c r="F43" s="8" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Step 1</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Scan the code above</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr"/>
-      <c r="E44" s="8" t="inlineStr"/>
-      <c r="F44" s="8" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>Step 2</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>Open the email we just sent</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr"/>
-      <c r="E45" s="8" t="inlineStr"/>
-      <c r="F45" s="8" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Step 3</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>Scan your badge at the booth to see and discuss your result</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr"/>
-      <c r="E46" s="8" t="inlineStr"/>
-      <c r="F46" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5153,266 +4224,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="76" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Matched from the job title on the visitor's badge. Keywords are matched as substrings, case-insensitive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Telling someone their job changes is the most personal claim the kiosk makes. Worth a close read.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Badge keyword match</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Role today</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Role in five years</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Focus pools</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>How the role changes</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Approved? (Y/N)</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Revised copy</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Client comments</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>underwrit, risk, appetite</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Underwriter</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>AI-Augmented Risk Advisor</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Process AI, Data for AI, AI Trust</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Shifts from data gathering and manual risk assessment to overseeing AI-driven risk models, concentrating human judgment on the complex and novel risks where model confidence is low.</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>claim, adjust, loss, fnol</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Claims Adjuster</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>AI-Assisted Decision Maker</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Process AI, Physical AI, Data for AI</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>Moves from end-to-end case management to exception handling and complex case oversight, with AI managing routine assessment, documentation and settlement.</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>actuar, pricing, reserv, model</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Actuary</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>AI Model Steward</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Data for AI, AI Trust, AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Evolves from building models to validating, governing and continuously improving AI pricing and reserving models, with explainability and fairness as core responsibilities.</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="8" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>distribut, sales, growth, agency, channel</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Distribution Manager</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>AI-Enabled Growth Leader</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Data for AI, Process AI, AI Strategy &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>Gains real-time performance intelligence, AI-powered lead scoring and agent copilot tools, shifting from reactive support to proactive growth enablement.</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>broker, agent, advis, placement</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Broker / Agent</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>AI-Powered Advisory Partner</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Process AI, Data for AI, Agentic Legacy Modernization</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Shifts from manual quote comparison and paperwork-intensive placement to relationship-led advisory, with AI streamlining quote aggregation, risk matching and proposal creation.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="8" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>(fallback, no keyword match)</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Insurance Leader</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>AI Portfolio Owner</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>AI Strategy &amp; Engineering, AI Trust, Agentic Legacy Modernization</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>Accountability moves from approving individual AI initiatives to owning an operating model, where governance, value tracking and workforce readiness are the levers that determine whether AI scales.</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5428,7 +4239,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Fine print on the results screen and the final screen currently reads: "Benchmark to be sourced from Gartner research. The comparison figures shown are illustrative placeholders, not Gartner data."</t>
+          <t>Fine print on the results screen and the final screen currently reads: "Benchmark to be sourced from Gartner research. Figures shown are illustrative placeholders."</t>
         </is>
       </c>
     </row>
@@ -5609,7 +4420,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5728,4 +4539,865 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="86" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Fixed copy that is not pool- or score-specific. Square brackets are filled in live by the kiosk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Approved? (Y/N)</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Revised copy</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Client comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Attract</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Eyebrow</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>AI-First Value Framework</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Attract</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Headline</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Are you ready to unlock your AI Value in insurance?</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Attract</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Subhead</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Two minutes. Six value pools. One blueprint.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Attract</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Touch cue</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Touch to begin</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>All screens</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Brand line</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Unlock AI Value in Insurance</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Framework screen</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Eyebrow</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>An Infosys framework</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Framework screen</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Headline</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Six pools of AI value in insurance</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Framework screen</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Lede</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Infosys' own model for insurance, not an industry standard. Each pool is somewhere AI creates measurable value for carriers, and somewhere programmes commonly stall.</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr"/>
+      <c r="E11" s="8" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Framework screen</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Gist: AI Strategy &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>One operating model, instead of pilots scattered across the business</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr"/>
+      <c r="E12" s="8" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Framework screen</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Gist: Data for AI</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Policy, claims and treaty data made AI-ready and audit-ready</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="8" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Framework screen</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Gist: Process AI</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Whole journeys redesigned, not task-level automation inside old ones</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="8" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Framework screen</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Gist: Agentic Legacy Modernization</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Core platforms modernised module by module, while the book stays live</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="8" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Framework screen</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Gist: Physical AI</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Telematics, IoT and drone data as a pricing and claims input</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="8" t="inlineStr"/>
+      <c r="F16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Framework screen</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Gist: AI Trust</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Explainability, bias testing and audit trails built in from the start</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="8" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Framework screen</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Button (primary)</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Explore the six pools</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="8" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Framework screen</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Button (secondary)</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Start the diagnostic</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="8" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Explore</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Tap a value pool to explore</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="8" t="inlineStr"/>
+      <c r="F20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Explore</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Start the diagnostic</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="8" t="inlineStr"/>
+      <c r="F21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Progress</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Question 1 of 6</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="8" t="inlineStr"/>
+      <c r="F22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Case card eyebrow</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>[Value pool] · [Client]</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="8" t="inlineStr"/>
+      <c r="F23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Case card link</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Read the case</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="8" t="inlineStr"/>
+      <c r="F24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Email capture</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Headline</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Where should we send it?</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="8" t="inlineStr"/>
+      <c r="F25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Email capture</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Lede</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>One address. Your blueprint lands in your inbox.</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="8" t="inlineStr"/>
+      <c r="F26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Email capture</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Field label</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="8" t="inlineStr"/>
+      <c r="F27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Email capture</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Field placeholder</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>name@company.com</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="8" t="inlineStr"/>
+      <c r="F28" s="8" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Email capture</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>See my results</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="8" t="inlineStr"/>
+      <c r="F29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Email capture</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Enter a valid email address.</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="8" t="inlineStr"/>
+      <c r="F30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Email capture</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Confirmation headline</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Got it</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="8" t="inlineStr"/>
+      <c r="F31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Email capture</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Confirmation body</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Your blueprint is on its way to [email]. Here is what it says.</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="8" t="inlineStr"/>
+      <c r="F32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Results 1</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Eyebrow</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Your position</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr"/>
+      <c r="E33" s="8" t="inlineStr"/>
+      <c r="F33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Results 2</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Headline</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Against the benchmark</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr"/>
+      <c r="E34" s="8" t="inlineStr"/>
+      <c r="F34" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Results 3</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Eyebrow</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Five-year view</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr"/>
+      <c r="E35" s="8" t="inlineStr"/>
+      <c r="F35" s="8" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Results 3</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Headline</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Where the gap goes</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr"/>
+      <c r="E36" s="8" t="inlineStr"/>
+      <c r="F36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Results 3</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Lede</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Unchanged, this is your five-year position.</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr"/>
+      <c r="E37" s="8" t="inlineStr"/>
+      <c r="F37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Eyebrow</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Report dispatched</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr"/>
+      <c r="E38" s="8" t="inlineStr"/>
+      <c r="F38" s="8" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Headline</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>On its way</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr"/>
+      <c r="E39" s="8" t="inlineStr"/>
+      <c r="F39" s="8" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Body</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Sent to [email]. Three ways to get it back:</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr"/>
+      <c r="E40" s="8" t="inlineStr"/>
+      <c r="F40" s="8" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Step 1</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Scan the code above</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr"/>
+      <c r="E41" s="8" t="inlineStr"/>
+      <c r="F41" s="8" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Step 2</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Open the email we just sent</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr"/>
+      <c r="E42" s="8" t="inlineStr"/>
+      <c r="F42" s="8" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Scan your badge at the booth to see and discuss your result</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr"/>
+      <c r="E43" s="8" t="inlineStr"/>
+      <c r="F43" s="8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Unlock AI Value - content for client review.xlsx
+++ b/Unlock AI Value - content for client review.xlsx
@@ -5030,7 +5030,7 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Where should we send it?</t>
+          <t>Your blueprint is ready</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr"/>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>One address. Your blueprint lands in your inbox.</t>
+          <t>Add your email and we will send the full report, with the case studies behind every score.</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr"/>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Work email</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr"/>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Got it</t>
+          <t>Your blueprint is on its way</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr"/>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Your blueprint is on its way to [email]. Here is what it says.</t>
+          <t>Sent to [email]. Your results are next.</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr"/>

--- a/Unlock AI Value - content for client review.xlsx
+++ b/Unlock AI Value - content for client review.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Score band feedback" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archetypes" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast lines" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Five-year view" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screen copy" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
@@ -527,7 +527,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Insurance kiosk · exported 02 September 2026 from the build's content model</t>
+          <t>Insurance kiosk · exported 03 September 2026 from the build's content model</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
     <row r="30" ht="14" customHeight="1">
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Forecast lines          The three five-year outlook captions.</t>
+          <t xml:space="preserve">    Five-year view          One paragraph per archetype for the last results screen.</t>
         </is>
       </c>
     </row>
@@ -4426,12 +4426,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="86" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="96" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
@@ -4440,101 +4440,155 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Captions on the five-year view.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Applies to</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
+          <t>The last results screen. One paragraph per archetype, replacing the three-column compounding / holding / exposed grid, per the note asking for a single paragraph in a persona style.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>{lead} and {lag} are filled in live with that visitor's strongest and weakest value pool, so the paragraph names their own pools rather than describing their category. Both always appear and are always different pools. Keep both tokens if you rewrite a paragraph.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>These are about trajectory on purpose, not about position. 'Your position' on the first results screen already says where someone is and what the risk is, so repeating it here would be the third time the report makes the same point.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Archetype</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Caption</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Paragraph</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Approved? (Y/N)</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Revised copy</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Client comments</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Pools where they score well</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>compounding</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Where your advantage widens. Each use case in a mature pool costs less than the last.</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Pools where they score badly</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>exposed</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Where the gap grows fastest, not because it degrades, but because the benchmark moves while it stays flat.</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Pools in the middle</t>
+          <t>Foundation First</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>foundation</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Enough capability to move, not to compound. A decision this year changes the five-year position.</t>
+          <t>Nothing here is behind yet, because nothing has been committed. Five years changes that twice over: the carriers that sequence the foundation first are running production models on shared data, and the ones that led with a visible pilot are rebuilding underneath it. {lag} is what decides which of those you become.</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr"/>
       <c r="F6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Pilot Purgatory</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>purgatory</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>On this trajectory the proofs keep proving the same point for another five years. The cost of each one does not fall, because every pilot rebuilds the pipeline the last one used, and each stall makes the next business case harder to fund. {lag} is the constraint that decides it, not the models. Clear that and {lead} becomes the platform everything else runs on.</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Point-Solution Myopia</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>myopia</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>{lead} keeps delivering, and that is the trap. Five years of local wins on separate pipelines leaves a set of integrations nobody owns and a cost per use case that never comes down. Carriers that consolidate onto shared data reach their eleventh use case for a fraction of what the first one cost. {lag} is where that has to start.</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Platform Without Purpose</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>The capability stays ahead of the benchmark. What changes over five years is the argument: an underused platform is the hardest investment to defend at budget, and it gets harder every cycle it is not pointed at underwriting or claims. {lag} is where the economics accrue, and {lead} is what you already have to spend on it.</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Enterprise Compounding</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>compounding</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>On this trajectory the gap widens in your favour, because each use case in a mature pool costs less than the last. The five-year constraint is not technology. It is whether underwriters act on the models: {lead} is already running, and {lag} is where reach or trust still limits what it is allowed to decide.</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4547,7 +4601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5265,12 +5319,12 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Lede</t>
+          <t>Paragraph</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Unchanged, this is your five-year position.</t>
+          <t>One per archetype, see the 'Five-year view' sheet</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr"/>
@@ -5280,17 +5334,17 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Results 3</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Eyebrow</t>
+          <t>Proof label</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Report dispatched</t>
+          <t>Proven now · [Value pool]</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr"/>
@@ -5305,12 +5359,12 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Headline</t>
+          <t>Eyebrow</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>On its way</t>
+          <t>Report dispatched</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr"/>
@@ -5325,12 +5379,12 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>Headline</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Sent to [email]. Three ways to get it back:</t>
+          <t>On its way</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr"/>
@@ -5345,12 +5399,12 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Step 1</t>
+          <t>Body</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Scan the code above</t>
+          <t>Sent to [email]. Three ways to get it back:</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr"/>
@@ -5365,12 +5419,12 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Step 2</t>
+          <t>Step 1</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Open the email we just sent</t>
+          <t>Scan the code above</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr"/>
@@ -5385,17 +5439,37 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Step 3</t>
+          <t>Step 2</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Scan your badge at the booth to see and discuss your result</t>
+          <t>Open the email we just sent</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr"/>
       <c r="E43" s="8" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Scan your badge at the booth to see and discuss your result</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr"/>
+      <c r="E44" s="8" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Unlock AI Value - content for client review.xlsx
+++ b/Unlock AI Value - content for client review.xlsx
@@ -4601,7 +4601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4659,12 +4659,12 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Eyebrow</t>
+          <t>Headline</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>AI-First Value Framework</t>
+          <t>Are you ready to unlock your AI Value in insurance?</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr"/>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Headline</t>
+          <t>Touch cue</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Are you ready to unlock your AI Value in insurance?</t>
+          <t>Touch to begin</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr"/>
@@ -4694,17 +4694,17 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Attract</t>
+          <t>All screens</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Subhead</t>
+          <t>Brand line</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Two minutes. Six value pools. One blueprint.</t>
+          <t>Unlock AI Value in Insurance</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr"/>
@@ -4714,17 +4714,17 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Attract</t>
+          <t>Framework screen</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Touch cue</t>
+          <t>Eyebrow</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Touch to begin</t>
+          <t>An Infosys framework</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr"/>
@@ -4734,17 +4734,17 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>All screens</t>
+          <t>Framework screen</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Brand line</t>
+          <t>Headline</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Unlock AI Value in Insurance</t>
+          <t>Six pools of AI value in insurance</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr"/>
@@ -4759,12 +4759,12 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Eyebrow</t>
+          <t>Lede</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>An Infosys framework</t>
+          <t>Infosys' own model for insurance, not an industry standard. Each pool is somewhere AI creates measurable value for carriers, and somewhere programmes commonly stall.</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr"/>
@@ -4779,12 +4779,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Headline</t>
+          <t>Gist: AI Strategy &amp; Engineering</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Six pools of AI value in insurance</t>
+          <t>One operating model, instead of pilots scattered across the business</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr"/>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Lede</t>
+          <t>Gist: Data for AI</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Infosys' own model for insurance, not an industry standard. Each pool is somewhere AI creates measurable value for carriers, and somewhere programmes commonly stall.</t>
+          <t>Policy, claims and treaty data made AI-ready and audit-ready</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr"/>
@@ -4819,12 +4819,12 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Gist: AI Strategy &amp; Engineering</t>
+          <t>Gist: Process AI</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>One operating model, instead of pilots scattered across the business</t>
+          <t>Whole journeys redesigned, not task-level automation inside old ones</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr"/>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Gist: Data for AI</t>
+          <t>Gist: Agentic Legacy Modernization</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Policy, claims and treaty data made AI-ready and audit-ready</t>
+          <t>Core platforms modernised module by module, while the book stays live</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr"/>
@@ -4859,12 +4859,12 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Gist: Process AI</t>
+          <t>Gist: Physical AI</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Whole journeys redesigned, not task-level automation inside old ones</t>
+          <t>Telematics, IoT and drone data as a pricing and claims input</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr"/>
@@ -4879,12 +4879,12 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Gist: Agentic Legacy Modernization</t>
+          <t>Gist: AI Trust</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Core platforms modernised module by module, while the book stays live</t>
+          <t>Explainability, bias testing and audit trails built in from the start</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr"/>
@@ -4899,12 +4899,12 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Gist: Physical AI</t>
+          <t>Button (primary)</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Telematics, IoT and drone data as a pricing and claims input</t>
+          <t>Explore the six pools</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr"/>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Gist: AI Trust</t>
+          <t>Button (secondary)</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Explainability, bias testing and audit trails built in from the start</t>
+          <t>Start the diagnostic</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr"/>
@@ -4934,17 +4934,17 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Framework screen</t>
+          <t>Explore</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Button (primary)</t>
+          <t>Instruction</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Explore the six pools</t>
+          <t>Tap a value pool to explore</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr"/>
@@ -4954,12 +4954,12 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Framework screen</t>
+          <t>Explore</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Button (secondary)</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -4974,17 +4974,17 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Explore</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Instruction</t>
+          <t>Progress</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Tap a value pool to explore</t>
+          <t>Question 1 of 6</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr"/>
@@ -4994,17 +4994,17 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Explore</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Case card eyebrow</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Start the diagnostic</t>
+          <t>[Value pool] · [Client]</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr"/>
@@ -5019,12 +5019,12 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Case card link</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Question 1 of 6</t>
+          <t>Read the case</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr"/>
@@ -5034,17 +5034,17 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Email capture</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Case card eyebrow</t>
+          <t>Headline</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>[Value pool] · [Client]</t>
+          <t>Your blueprint is ready</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr"/>
@@ -5054,17 +5054,17 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Email capture</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Case card link</t>
+          <t>Lede</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Read the case</t>
+          <t>Add your email and we will send the full report, with the case studies behind every score.</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr"/>
@@ -5079,12 +5079,12 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Headline</t>
+          <t>Field label</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Your blueprint is ready</t>
+          <t>Work email</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr"/>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Lede</t>
+          <t>Field placeholder</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Add your email and we will send the full report, with the case studies behind every score.</t>
+          <t>name@company.com</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr"/>
@@ -5119,12 +5119,12 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Field label</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Work email</t>
+          <t>See my results</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr"/>
@@ -5139,12 +5139,12 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Field placeholder</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>name@company.com</t>
+          <t>Enter a valid email address.</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr"/>
@@ -5159,12 +5159,12 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Confirmation headline</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>See my results</t>
+          <t>Your blueprint is on its way</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr"/>
@@ -5179,12 +5179,12 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Confirmation body</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Enter a valid email address.</t>
+          <t>Sent to [email]. Your results are next.</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr"/>
@@ -5194,17 +5194,17 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Email capture</t>
+          <t>Results 1</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Confirmation headline</t>
+          <t>Eyebrow</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Your blueprint is on its way</t>
+          <t>Your position</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr"/>
@@ -5214,17 +5214,17 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Email capture</t>
+          <t>Results 2</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Confirmation body</t>
+          <t>Headline</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Sent to [email]. Your results are next.</t>
+          <t>Against the benchmark</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr"/>
@@ -5234,7 +5234,7 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Results 1</t>
+          <t>Results 3</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Your position</t>
+          <t>Five-year view</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr"/>
@@ -5254,7 +5254,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Results 2</t>
+          <t>Results 3</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Against the benchmark</t>
+          <t>Where the gap goes</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr"/>
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Eyebrow</t>
+          <t>Paragraph</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Five-year view</t>
+          <t>One per archetype, see the 'Five-year view' sheet</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr"/>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Headline</t>
+          <t>Proof label</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Where the gap goes</t>
+          <t>Proven now · [Value pool]</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr"/>
@@ -5314,17 +5314,17 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Results 3</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Paragraph</t>
+          <t>Eyebrow</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>One per archetype, see the 'Five-year view' sheet</t>
+          <t>Report dispatched</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr"/>
@@ -5334,17 +5334,17 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Results 3</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Proof label</t>
+          <t>Headline</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Proven now · [Value pool]</t>
+          <t>On its way</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr"/>
@@ -5359,12 +5359,12 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Eyebrow</t>
+          <t>Body</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Report dispatched</t>
+          <t>Sent to [email]. Three ways to get it back:</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr"/>
@@ -5379,12 +5379,12 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Headline</t>
+          <t>Step 1</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>On its way</t>
+          <t>Scan the code above</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr"/>
@@ -5399,12 +5399,12 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>Step 2</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Sent to [email]. Three ways to get it back:</t>
+          <t>Open the email we just sent</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr"/>
@@ -5419,57 +5419,17 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Step 1</t>
+          <t>Step 3</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Scan the code above</t>
+          <t>Scan your badge at the booth to see and discuss your result</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr"/>
       <c r="E42" s="8" t="inlineStr"/>
       <c r="F42" s="8" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>Step 2</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Open the email we just sent</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr"/>
-      <c r="E43" s="8" t="inlineStr"/>
-      <c r="F43" s="8" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Step 3</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Scan your badge at the booth to see and discuss your result</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr"/>
-      <c r="E44" s="8" t="inlineStr"/>
-      <c r="F44" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
